--- a/extraction_script/data/صورتهاي مالي 1398.xlsx
+++ b/extraction_script/data/صورتهاي مالي 1398.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Armin KHoojavi\Downloads\persian-smart-accounting1\extraction_script\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D11320-BA90-47CE-BF05-178F525F937A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E53FD8A-0C1E-4756-BA57-81798363A3F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="944" firstSheet="13" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="16200" tabRatio="944" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="فهرست" sheetId="26" r:id="rId1"/>
@@ -4701,7 +4701,7 @@
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="101" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="915">
+  <cellXfs count="918">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="43" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6838,273 +6838,273 @@
     <xf numFmtId="3" fontId="140" fillId="43" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="10" xfId="37" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="21" xfId="37" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="39" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="10" xfId="39" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="50" fillId="0" borderId="10" xfId="37" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="50" fillId="0" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="43" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="12" xfId="37" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="12" xfId="37" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="113" fillId="0" borderId="12" xfId="37" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="142" fillId="0" borderId="12" xfId="37" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="83" fillId="0" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="0" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="83" fillId="0" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="83" fillId="0" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="120" fillId="0" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="46" fillId="0" borderId="0" xfId="52" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="52" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="10" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="27" borderId="27" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="27" borderId="28" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="27" borderId="25" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="27" borderId="26" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="27" borderId="23" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="27" borderId="20" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="27" borderId="24" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="27" borderId="12" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="12" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="27" borderId="12" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="89" fillId="0" borderId="0" xfId="54" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="18" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="13" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="38" borderId="18" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="38" borderId="13" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="38" borderId="18" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="38" borderId="13" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="38" borderId="18" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="38" borderId="13" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="38" borderId="23" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="38" borderId="20" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="89" fillId="0" borderId="10" xfId="54" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="12" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="38" borderId="12" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="38" borderId="12" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="10" xfId="37" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="39" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="10" xfId="39" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="50" fillId="0" borderId="10" xfId="37" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="50" fillId="0" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="23" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="43" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="12" xfId="37" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="12" xfId="37" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="113" fillId="0" borderId="12" xfId="37" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="142" fillId="0" borderId="12" xfId="37" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="83" fillId="0" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="29" fillId="0" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="83" fillId="0" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="83" fillId="0" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="120" fillId="0" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="46" fillId="0" borderId="0" xfId="52" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="52" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="10" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="27" borderId="27" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="27" borderId="28" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="27" borderId="25" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="27" borderId="26" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="27" borderId="23" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="27" borderId="20" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="27" borderId="24" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="27" borderId="12" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="12" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="27" borderId="12" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="89" fillId="0" borderId="0" xfId="54" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="18" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="13" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="38" borderId="18" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="38" borderId="13" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="38" borderId="18" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="38" borderId="13" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="38" borderId="18" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="38" borderId="13" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="38" borderId="23" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="38" borderId="20" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="89" fillId="0" borderId="10" xfId="54" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="12" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="23" fillId="38" borderId="12" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="3" fontId="23" fillId="38" borderId="12" xfId="54" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="21" xfId="37" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="37" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7289,6 +7289,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="50" fillId="39" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="116" fillId="39" borderId="0" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="27" fillId="39" borderId="10" xfId="37" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -11668,7 +11677,7 @@
                     <c:extLst>
                       <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                       <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                        <c16:uniqueId val="{00000000-4FB5-4DAC-9CDC-5739E93B2B6E}"/>
+                        <c16:uniqueId val="{00000000-311C-4DB6-864F-50A0A1383336}"/>
                       </c:ext>
                     </c:extLst>
                   </c15:dLbl>
@@ -11990,7 +11999,7 @@
                     <c:extLst>
                       <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                       <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                        <c16:uniqueId val="{00000001-4FB5-4DAC-9CDC-5739E93B2B6E}"/>
+                        <c16:uniqueId val="{00000001-311C-4DB6-864F-50A0A1383336}"/>
                       </c:ext>
                     </c:extLst>
                   </c15:dLbl>
@@ -12166,7 +12175,7 @@
                     <c:extLst>
                       <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                       <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                        <c16:uniqueId val="{00000002-4FB5-4DAC-9CDC-5739E93B2B6E}"/>
+                        <c16:uniqueId val="{00000002-311C-4DB6-864F-50A0A1383336}"/>
                       </c:ext>
                     </c:extLst>
                   </c15:dLbl>
@@ -19913,17 +19922,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="42.75" customHeight="1">
-      <c r="A1" s="770" t="s">
+      <c r="A1" s="771" t="s">
         <v>500</v>
       </c>
-      <c r="B1" s="770"/>
-      <c r="C1" s="770"/>
-      <c r="D1" s="770"/>
-      <c r="E1" s="770"/>
-      <c r="F1" s="770"/>
-      <c r="G1" s="770"/>
-      <c r="H1" s="770"/>
-      <c r="I1" s="770"/>
+      <c r="B1" s="771"/>
+      <c r="C1" s="771"/>
+      <c r="D1" s="771"/>
+      <c r="E1" s="771"/>
+      <c r="F1" s="771"/>
+      <c r="G1" s="771"/>
+      <c r="H1" s="771"/>
+      <c r="I1" s="771"/>
     </row>
     <row r="2" spans="1:9" ht="25.5" customHeight="1">
       <c r="A2" s="438"/>
@@ -19991,13 +20000,13 @@
     <row r="7" spans="1:9" ht="27">
       <c r="A7" s="438"/>
       <c r="B7" s="438"/>
-      <c r="C7" s="771" t="s">
+      <c r="C7" s="772" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="771"/>
-      <c r="E7" s="771"/>
-      <c r="F7" s="771"/>
-      <c r="G7" s="771"/>
+      <c r="D7" s="772"/>
+      <c r="E7" s="772"/>
+      <c r="F7" s="772"/>
+      <c r="G7" s="772"/>
       <c r="H7" s="438"/>
       <c r="I7" s="444" t="s">
         <v>24</v>
@@ -20209,28 +20218,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="65.25" customHeight="1">
-      <c r="A1" s="821" t="s">
+      <c r="A1" s="822" t="s">
         <v>729</v>
       </c>
-      <c r="B1" s="821"/>
-      <c r="C1" s="821"/>
-      <c r="D1" s="821"/>
-      <c r="E1" s="821"/>
-      <c r="F1" s="821"/>
-      <c r="G1" s="821"/>
-      <c r="H1" s="821"/>
-      <c r="I1" s="821"/>
-      <c r="J1" s="821"/>
-      <c r="K1" s="821"/>
-      <c r="L1" s="821"/>
+      <c r="B1" s="822"/>
+      <c r="C1" s="822"/>
+      <c r="D1" s="822"/>
+      <c r="E1" s="822"/>
+      <c r="F1" s="822"/>
+      <c r="G1" s="822"/>
+      <c r="H1" s="822"/>
+      <c r="I1" s="822"/>
+      <c r="J1" s="822"/>
+      <c r="K1" s="822"/>
+      <c r="L1" s="822"/>
     </row>
     <row r="2" spans="1:15" ht="44.25" customHeight="1">
-      <c r="A2" s="822" t="s">
+      <c r="A2" s="823" t="s">
         <v>430</v>
       </c>
-      <c r="B2" s="822"/>
-      <c r="C2" s="822"/>
-      <c r="D2" s="822"/>
+      <c r="B2" s="823"/>
+      <c r="C2" s="823"/>
+      <c r="D2" s="823"/>
       <c r="E2" s="430"/>
       <c r="F2" s="430"/>
       <c r="G2" s="430"/>
@@ -20241,34 +20250,34 @@
       <c r="L2" s="431"/>
     </row>
     <row r="3" spans="1:15" s="300" customFormat="1" ht="66.75" customHeight="1">
-      <c r="A3" s="823" t="s">
+      <c r="A3" s="824" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="824"/>
-      <c r="C3" s="827" t="s">
+      <c r="B3" s="825"/>
+      <c r="C3" s="828" t="s">
         <v>431</v>
       </c>
-      <c r="D3" s="828"/>
-      <c r="E3" s="827" t="s">
+      <c r="D3" s="829"/>
+      <c r="E3" s="828" t="s">
         <v>432</v>
       </c>
-      <c r="F3" s="828"/>
-      <c r="G3" s="827" t="s">
+      <c r="F3" s="829"/>
+      <c r="G3" s="828" t="s">
         <v>433</v>
       </c>
-      <c r="H3" s="829"/>
-      <c r="I3" s="827" t="s">
+      <c r="H3" s="830"/>
+      <c r="I3" s="828" t="s">
         <v>434</v>
       </c>
-      <c r="J3" s="829"/>
-      <c r="K3" s="830" t="s">
+      <c r="J3" s="830"/>
+      <c r="K3" s="831" t="s">
         <v>435</v>
       </c>
-      <c r="L3" s="830"/>
+      <c r="L3" s="831"/>
     </row>
     <row r="4" spans="1:15" s="301" customFormat="1" ht="35.25" customHeight="1">
-      <c r="A4" s="825"/>
-      <c r="B4" s="826"/>
+      <c r="A4" s="826"/>
+      <c r="B4" s="827"/>
       <c r="C4" s="432" t="s">
         <v>449</v>
       </c>
@@ -20301,10 +20310,10 @@
       </c>
     </row>
     <row r="5" spans="1:15" s="302" customFormat="1" ht="58.5" customHeight="1">
-      <c r="A5" s="831" t="s">
+      <c r="A5" s="832" t="s">
         <v>436</v>
       </c>
-      <c r="B5" s="831"/>
+      <c r="B5" s="832"/>
       <c r="C5" s="433">
         <f>94000000+42500000+22500000</f>
         <v>159000000</v>
@@ -20347,10 +20356,10 @@
       <c r="O5"/>
     </row>
     <row r="6" spans="1:15" s="302" customFormat="1" ht="58.5" customHeight="1">
-      <c r="A6" s="831" t="s">
+      <c r="A6" s="832" t="s">
         <v>437</v>
       </c>
-      <c r="B6" s="831"/>
+      <c r="B6" s="832"/>
       <c r="C6" s="433">
         <v>93000000</v>
       </c>
@@ -20391,10 +20400,10 @@
       <c r="O6"/>
     </row>
     <row r="7" spans="1:15" s="302" customFormat="1" ht="58.5" customHeight="1">
-      <c r="A7" s="831" t="s">
+      <c r="A7" s="832" t="s">
         <v>438</v>
       </c>
-      <c r="B7" s="831"/>
+      <c r="B7" s="832"/>
       <c r="C7" s="433">
         <f>420102535+25000000</f>
         <v>445102535</v>
@@ -20437,10 +20446,10 @@
       <c r="O7"/>
     </row>
     <row r="8" spans="1:15" s="302" customFormat="1" ht="58.5" customHeight="1">
-      <c r="A8" s="831" t="s">
+      <c r="A8" s="832" t="s">
         <v>439</v>
       </c>
-      <c r="B8" s="831"/>
+      <c r="B8" s="832"/>
       <c r="C8" s="433">
         <v>0</v>
       </c>
@@ -20475,10 +20484,10 @@
       </c>
     </row>
     <row r="9" spans="1:15" s="302" customFormat="1" ht="58.5" customHeight="1">
-      <c r="A9" s="831" t="s">
+      <c r="A9" s="832" t="s">
         <v>440</v>
       </c>
-      <c r="B9" s="831"/>
+      <c r="B9" s="832"/>
       <c r="C9" s="433">
         <v>2531019824</v>
       </c>
@@ -20516,10 +20525,10 @@
       </c>
     </row>
     <row r="10" spans="1:15" s="302" customFormat="1" ht="58.5" customHeight="1">
-      <c r="A10" s="831" t="s">
+      <c r="A10" s="832" t="s">
         <v>441</v>
       </c>
-      <c r="B10" s="831"/>
+      <c r="B10" s="832"/>
       <c r="C10" s="433">
         <v>0</v>
       </c>
@@ -20554,10 +20563,10 @@
       </c>
     </row>
     <row r="11" spans="1:15" s="302" customFormat="1" ht="44.25" customHeight="1">
-      <c r="A11" s="832" t="s">
+      <c r="A11" s="833" t="s">
         <v>142</v>
       </c>
-      <c r="B11" s="832"/>
+      <c r="B11" s="833"/>
       <c r="C11" s="434">
         <f>SUM(C5:C10)</f>
         <v>3228122359</v>
@@ -20621,10 +20630,10 @@
       <c r="A13" s="735"/>
       <c r="B13" s="743"/>
       <c r="C13" s="741"/>
-      <c r="D13" s="820">
+      <c r="D13" s="821">
         <v>13</v>
       </c>
-      <c r="E13" s="820"/>
+      <c r="E13" s="821"/>
       <c r="F13" s="741"/>
       <c r="G13" s="744"/>
       <c r="H13" s="744"/>
@@ -21643,48 +21652,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="53.25" customHeight="1">
-      <c r="A1" s="833" t="s">
+      <c r="A1" s="834" t="s">
         <v>975</v>
       </c>
-      <c r="B1" s="833"/>
-      <c r="C1" s="833"/>
-      <c r="D1" s="833"/>
-      <c r="E1" s="833"/>
-      <c r="F1" s="833"/>
+      <c r="B1" s="834"/>
+      <c r="C1" s="834"/>
+      <c r="D1" s="834"/>
+      <c r="E1" s="834"/>
+      <c r="F1" s="834"/>
     </row>
     <row r="2" spans="1:12" ht="28.5">
-      <c r="A2" s="844" t="s">
+      <c r="A2" s="845" t="s">
         <v>857</v>
       </c>
-      <c r="B2" s="844"/>
-      <c r="C2" s="844"/>
-      <c r="D2" s="844"/>
-      <c r="E2" s="844"/>
-      <c r="F2" s="844"/>
+      <c r="B2" s="845"/>
+      <c r="C2" s="845"/>
+      <c r="D2" s="845"/>
+      <c r="E2" s="845"/>
+      <c r="F2" s="845"/>
     </row>
     <row r="3" spans="1:12" s="124" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A3" s="834" t="s">
+      <c r="A3" s="835" t="s">
         <v>444</v>
       </c>
-      <c r="B3" s="836" t="s">
+      <c r="B3" s="837" t="s">
         <v>445</v>
       </c>
-      <c r="C3" s="838" t="s">
+      <c r="C3" s="839" t="s">
         <v>446</v>
       </c>
-      <c r="D3" s="840" t="s">
+      <c r="D3" s="841" t="s">
         <v>447</v>
       </c>
-      <c r="E3" s="842" t="s">
+      <c r="E3" s="843" t="s">
         <v>448</v>
       </c>
-      <c r="F3" s="843"/>
+      <c r="F3" s="844"/>
     </row>
     <row r="4" spans="1:12" s="124" customFormat="1" ht="25.5">
-      <c r="A4" s="835"/>
-      <c r="B4" s="837"/>
-      <c r="C4" s="839"/>
-      <c r="D4" s="841"/>
+      <c r="A4" s="836"/>
+      <c r="B4" s="838"/>
+      <c r="C4" s="840"/>
+      <c r="D4" s="842"/>
       <c r="E4" s="478" t="s">
         <v>449</v>
       </c>
@@ -24230,48 +24239,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="52.5" customHeight="1">
-      <c r="A1" s="833" t="s">
+      <c r="A1" s="834" t="s">
         <v>856</v>
       </c>
-      <c r="B1" s="833"/>
-      <c r="C1" s="833"/>
-      <c r="D1" s="833"/>
-      <c r="E1" s="833"/>
-      <c r="F1" s="833"/>
+      <c r="B1" s="834"/>
+      <c r="C1" s="834"/>
+      <c r="D1" s="834"/>
+      <c r="E1" s="834"/>
+      <c r="F1" s="834"/>
     </row>
     <row r="2" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A2" s="833" t="s">
+      <c r="A2" s="834" t="s">
         <v>857</v>
       </c>
-      <c r="B2" s="833"/>
-      <c r="C2" s="833"/>
-      <c r="D2" s="833"/>
-      <c r="E2" s="833"/>
-      <c r="F2" s="833"/>
+      <c r="B2" s="834"/>
+      <c r="C2" s="834"/>
+      <c r="D2" s="834"/>
+      <c r="E2" s="834"/>
+      <c r="F2" s="834"/>
     </row>
     <row r="3" spans="1:6" s="117" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A3" s="845" t="s">
+      <c r="A3" s="846" t="s">
         <v>444</v>
       </c>
-      <c r="B3" s="846" t="s">
+      <c r="B3" s="847" t="s">
         <v>445</v>
       </c>
-      <c r="C3" s="846" t="s">
+      <c r="C3" s="847" t="s">
         <v>446</v>
       </c>
-      <c r="D3" s="847" t="s">
+      <c r="D3" s="848" t="s">
         <v>479</v>
       </c>
-      <c r="E3" s="847" t="s">
+      <c r="E3" s="848" t="s">
         <v>448</v>
       </c>
-      <c r="F3" s="847"/>
+      <c r="F3" s="848"/>
     </row>
     <row r="4" spans="1:6" s="117" customFormat="1" ht="22.5">
-      <c r="A4" s="845"/>
-      <c r="B4" s="846"/>
-      <c r="C4" s="846"/>
-      <c r="D4" s="847"/>
+      <c r="A4" s="846"/>
+      <c r="B4" s="847"/>
+      <c r="C4" s="847"/>
+      <c r="D4" s="848"/>
       <c r="E4" s="470" t="s">
         <v>449</v>
       </c>
@@ -25976,61 +25985,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="30" customHeight="1">
-      <c r="A1" s="848" t="s">
+      <c r="A1" s="765" t="s">
         <v>960</v>
       </c>
-      <c r="B1" s="848"/>
-      <c r="C1" s="848"/>
-      <c r="D1" s="848"/>
-      <c r="E1" s="848"/>
-      <c r="F1" s="848"/>
-      <c r="G1" s="848"/>
-      <c r="H1" s="848"/>
-      <c r="I1" s="848"/>
-      <c r="J1" s="848"/>
-      <c r="K1" s="848"/>
-      <c r="L1" s="848"/>
-      <c r="M1" s="848"/>
-      <c r="N1" s="848"/>
-      <c r="O1" s="848"/>
+      <c r="B1" s="765"/>
+      <c r="C1" s="765"/>
+      <c r="D1" s="765"/>
+      <c r="E1" s="765"/>
+      <c r="F1" s="765"/>
+      <c r="G1" s="765"/>
+      <c r="H1" s="765"/>
+      <c r="I1" s="765"/>
+      <c r="J1" s="765"/>
+      <c r="K1" s="765"/>
+      <c r="L1" s="765"/>
+      <c r="M1" s="765"/>
+      <c r="N1" s="765"/>
+      <c r="O1" s="765"/>
     </row>
     <row r="2" spans="1:17" ht="30" customHeight="1">
-      <c r="A2" s="849" t="s">
+      <c r="A2" s="766" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="849"/>
-      <c r="C2" s="849"/>
-      <c r="D2" s="849"/>
-      <c r="E2" s="849"/>
-      <c r="F2" s="849"/>
-      <c r="G2" s="849"/>
-      <c r="H2" s="849"/>
-      <c r="I2" s="849"/>
-      <c r="J2" s="849"/>
-      <c r="K2" s="849"/>
-      <c r="L2" s="849"/>
-      <c r="M2" s="849"/>
-      <c r="N2" s="849"/>
-      <c r="O2" s="849"/>
+      <c r="B2" s="766"/>
+      <c r="C2" s="766"/>
+      <c r="D2" s="766"/>
+      <c r="E2" s="766"/>
+      <c r="F2" s="766"/>
+      <c r="G2" s="766"/>
+      <c r="H2" s="766"/>
+      <c r="I2" s="766"/>
+      <c r="J2" s="766"/>
+      <c r="K2" s="766"/>
+      <c r="L2" s="766"/>
+      <c r="M2" s="766"/>
+      <c r="N2" s="766"/>
+      <c r="O2" s="766"/>
     </row>
     <row r="3" spans="1:17" ht="30" customHeight="1">
-      <c r="A3" s="849" t="s">
+      <c r="A3" s="766" t="s">
         <v>730</v>
       </c>
-      <c r="B3" s="849"/>
-      <c r="C3" s="849"/>
-      <c r="D3" s="849"/>
-      <c r="E3" s="849"/>
-      <c r="F3" s="849"/>
-      <c r="G3" s="849"/>
-      <c r="H3" s="849"/>
-      <c r="I3" s="849"/>
-      <c r="J3" s="849"/>
-      <c r="K3" s="849"/>
-      <c r="L3" s="849"/>
-      <c r="M3" s="849"/>
-      <c r="N3" s="849"/>
-      <c r="O3" s="849"/>
+      <c r="B3" s="766"/>
+      <c r="C3" s="766"/>
+      <c r="D3" s="766"/>
+      <c r="E3" s="766"/>
+      <c r="F3" s="766"/>
+      <c r="G3" s="766"/>
+      <c r="H3" s="766"/>
+      <c r="I3" s="766"/>
+      <c r="J3" s="766"/>
+      <c r="K3" s="766"/>
+      <c r="L3" s="766"/>
+      <c r="M3" s="766"/>
+      <c r="N3" s="766"/>
+      <c r="O3" s="766"/>
     </row>
     <row r="4" spans="1:17" ht="30" customHeight="1">
       <c r="A4" s="268" t="s">
@@ -26052,46 +26061,46 @@
       <c r="O4" s="153"/>
     </row>
     <row r="5" spans="1:17" ht="43.5" customHeight="1">
-      <c r="A5" s="851" t="s">
+      <c r="A5" s="769" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="851"/>
-      <c r="C5" s="851"/>
-      <c r="D5" s="851"/>
-      <c r="E5" s="851"/>
-      <c r="F5" s="851"/>
-      <c r="G5" s="851"/>
-      <c r="H5" s="851"/>
-      <c r="I5" s="851"/>
-      <c r="J5" s="851"/>
-      <c r="K5" s="851"/>
-      <c r="L5" s="851"/>
-      <c r="M5" s="851"/>
-      <c r="N5" s="851"/>
-      <c r="O5" s="851"/>
+      <c r="B5" s="769"/>
+      <c r="C5" s="769"/>
+      <c r="D5" s="769"/>
+      <c r="E5" s="769"/>
+      <c r="F5" s="769"/>
+      <c r="G5" s="769"/>
+      <c r="H5" s="769"/>
+      <c r="I5" s="769"/>
+      <c r="J5" s="769"/>
+      <c r="K5" s="769"/>
+      <c r="L5" s="769"/>
+      <c r="M5" s="769"/>
+      <c r="N5" s="769"/>
+      <c r="O5" s="769"/>
     </row>
     <row r="6" spans="1:17" ht="30" customHeight="1">
       <c r="A6" s="140"/>
       <c r="B6" s="140"/>
       <c r="C6" s="140"/>
       <c r="D6" s="140"/>
-      <c r="E6" s="765" t="s">
+      <c r="E6" s="767" t="s">
         <v>95</v>
       </c>
-      <c r="F6" s="765"/>
-      <c r="G6" s="765"/>
-      <c r="H6" s="765"/>
+      <c r="F6" s="767"/>
+      <c r="G6" s="767"/>
+      <c r="H6" s="767"/>
       <c r="I6" s="140"/>
-      <c r="J6" s="765" t="s">
+      <c r="J6" s="767" t="s">
         <v>96</v>
       </c>
-      <c r="K6" s="765"/>
-      <c r="L6" s="765"/>
-      <c r="M6" s="765"/>
-      <c r="N6" s="765" t="s">
+      <c r="K6" s="767"/>
+      <c r="L6" s="767"/>
+      <c r="M6" s="767"/>
+      <c r="N6" s="767" t="s">
         <v>103</v>
       </c>
-      <c r="O6" s="765"/>
+      <c r="O6" s="767"/>
     </row>
     <row r="7" spans="1:17" ht="143.25" customHeight="1">
       <c r="A7" s="140"/>
@@ -26135,11 +26144,11 @@
       </c>
     </row>
     <row r="8" spans="1:17" ht="51.75" customHeight="1">
-      <c r="A8" s="850" t="s">
+      <c r="A8" s="768" t="s">
         <v>643</v>
       </c>
-      <c r="B8" s="850"/>
-      <c r="C8" s="850"/>
+      <c r="B8" s="768"/>
+      <c r="C8" s="768"/>
       <c r="D8" s="140" t="s">
         <v>495</v>
       </c>
@@ -26176,11 +26185,11 @@
       </c>
     </row>
     <row r="9" spans="1:17" ht="51.75" customHeight="1">
-      <c r="A9" s="852" t="s">
+      <c r="A9" s="770" t="s">
         <v>642</v>
       </c>
-      <c r="B9" s="852"/>
-      <c r="C9" s="852"/>
+      <c r="B9" s="770"/>
+      <c r="C9" s="770"/>
       <c r="D9" s="247" t="s">
         <v>496</v>
       </c>
@@ -26222,11 +26231,11 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="51.75" customHeight="1">
-      <c r="A10" s="852" t="s">
+      <c r="A10" s="770" t="s">
         <v>640</v>
       </c>
-      <c r="B10" s="852"/>
-      <c r="C10" s="852"/>
+      <c r="B10" s="770"/>
+      <c r="C10" s="770"/>
       <c r="D10" s="247" t="s">
         <v>663</v>
       </c>
@@ -26269,11 +26278,11 @@
       </c>
     </row>
     <row r="11" spans="1:17" ht="51.75" customHeight="1">
-      <c r="A11" s="852" t="s">
+      <c r="A11" s="770" t="s">
         <v>647</v>
       </c>
-      <c r="B11" s="852"/>
-      <c r="C11" s="852"/>
+      <c r="B11" s="770"/>
+      <c r="C11" s="770"/>
       <c r="D11" s="247" t="s">
         <v>664</v>
       </c>
@@ -26310,11 +26319,11 @@
       </c>
     </row>
     <row r="12" spans="1:17" ht="51.75" customHeight="1">
-      <c r="A12" s="852" t="s">
+      <c r="A12" s="770" t="s">
         <v>645</v>
       </c>
-      <c r="B12" s="852"/>
-      <c r="C12" s="852"/>
+      <c r="B12" s="770"/>
+      <c r="C12" s="770"/>
       <c r="D12" s="247" t="s">
         <v>669</v>
       </c>
@@ -26356,11 +26365,11 @@
       </c>
     </row>
     <row r="13" spans="1:17" ht="51.75" customHeight="1">
-      <c r="A13" s="852" t="s">
+      <c r="A13" s="770" t="s">
         <v>844</v>
       </c>
-      <c r="B13" s="852"/>
-      <c r="C13" s="852"/>
+      <c r="B13" s="770"/>
+      <c r="C13" s="770"/>
       <c r="D13" s="247"/>
       <c r="E13" s="647">
         <f>SUM(E8:E12)</f>
@@ -26459,13 +26468,13 @@
       </c>
     </row>
     <row r="16" spans="1:17" ht="41.25" customHeight="1" thickBot="1">
-      <c r="A16" s="851" t="s">
+      <c r="A16" s="769" t="s">
         <v>649</v>
       </c>
-      <c r="B16" s="851" t="s">
+      <c r="B16" s="769" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="851"/>
+      <c r="C16" s="769"/>
       <c r="D16" s="296"/>
       <c r="E16" s="238">
         <f>E15+E13</f>
@@ -26514,24 +26523,24 @@
       <c r="Q16" s="200"/>
     </row>
     <row r="17" spans="1:14" ht="30" customHeight="1" thickTop="1">
-      <c r="A17" s="811"/>
-      <c r="B17" s="811"/>
-      <c r="C17" s="811"/>
-      <c r="D17" s="811"/>
-      <c r="E17" s="811"/>
-      <c r="F17" s="811"/>
+      <c r="A17" s="764"/>
+      <c r="B17" s="764"/>
+      <c r="C17" s="764"/>
+      <c r="D17" s="764"/>
+      <c r="E17" s="764"/>
+      <c r="F17" s="764"/>
       <c r="G17" s="199"/>
       <c r="H17" s="199"/>
     </row>
     <row r="18" spans="1:14" ht="30" customHeight="1">
-      <c r="A18" s="811" t="s">
+      <c r="A18" s="764" t="s">
         <v>974</v>
       </c>
-      <c r="B18" s="811"/>
-      <c r="C18" s="811"/>
-      <c r="D18" s="811"/>
-      <c r="E18" s="811"/>
-      <c r="F18" s="811"/>
+      <c r="B18" s="764"/>
+      <c r="C18" s="764"/>
+      <c r="D18" s="764"/>
+      <c r="E18" s="764"/>
+      <c r="F18" s="764"/>
       <c r="G18" s="199"/>
       <c r="H18" s="199"/>
     </row>
@@ -26606,61 +26615,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="30" customHeight="1">
-      <c r="A1" s="767" t="s">
+      <c r="A1" s="851" t="s">
         <v>960</v>
       </c>
-      <c r="B1" s="767"/>
-      <c r="C1" s="767"/>
-      <c r="D1" s="767"/>
-      <c r="E1" s="767"/>
-      <c r="F1" s="767"/>
-      <c r="G1" s="767"/>
-      <c r="H1" s="767"/>
-      <c r="I1" s="767"/>
-      <c r="J1" s="767"/>
-      <c r="K1" s="767"/>
-      <c r="L1" s="767"/>
-      <c r="M1" s="767"/>
-      <c r="N1" s="767"/>
-      <c r="O1" s="767"/>
+      <c r="B1" s="851"/>
+      <c r="C1" s="851"/>
+      <c r="D1" s="851"/>
+      <c r="E1" s="851"/>
+      <c r="F1" s="851"/>
+      <c r="G1" s="851"/>
+      <c r="H1" s="851"/>
+      <c r="I1" s="851"/>
+      <c r="J1" s="851"/>
+      <c r="K1" s="851"/>
+      <c r="L1" s="851"/>
+      <c r="M1" s="851"/>
+      <c r="N1" s="851"/>
+      <c r="O1" s="851"/>
     </row>
     <row r="2" spans="1:17" ht="30" customHeight="1">
-      <c r="A2" s="768" t="s">
+      <c r="A2" s="784" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="768"/>
-      <c r="C2" s="768"/>
-      <c r="D2" s="768"/>
-      <c r="E2" s="768"/>
-      <c r="F2" s="768"/>
-      <c r="G2" s="768"/>
-      <c r="H2" s="768"/>
-      <c r="I2" s="768"/>
-      <c r="J2" s="768"/>
-      <c r="K2" s="768"/>
-      <c r="L2" s="768"/>
-      <c r="M2" s="768"/>
-      <c r="N2" s="768"/>
-      <c r="O2" s="768"/>
+      <c r="B2" s="784"/>
+      <c r="C2" s="784"/>
+      <c r="D2" s="784"/>
+      <c r="E2" s="784"/>
+      <c r="F2" s="784"/>
+      <c r="G2" s="784"/>
+      <c r="H2" s="784"/>
+      <c r="I2" s="784"/>
+      <c r="J2" s="784"/>
+      <c r="K2" s="784"/>
+      <c r="L2" s="784"/>
+      <c r="M2" s="784"/>
+      <c r="N2" s="784"/>
+      <c r="O2" s="784"/>
     </row>
     <row r="3" spans="1:17" ht="30" customHeight="1">
-      <c r="A3" s="768" t="s">
+      <c r="A3" s="784" t="s">
         <v>730</v>
       </c>
-      <c r="B3" s="768"/>
-      <c r="C3" s="768"/>
-      <c r="D3" s="768"/>
-      <c r="E3" s="768"/>
-      <c r="F3" s="768"/>
-      <c r="G3" s="768"/>
-      <c r="H3" s="768"/>
-      <c r="I3" s="768"/>
-      <c r="J3" s="768"/>
-      <c r="K3" s="768"/>
-      <c r="L3" s="768"/>
-      <c r="M3" s="768"/>
-      <c r="N3" s="768"/>
-      <c r="O3" s="768"/>
+      <c r="B3" s="784"/>
+      <c r="C3" s="784"/>
+      <c r="D3" s="784"/>
+      <c r="E3" s="784"/>
+      <c r="F3" s="784"/>
+      <c r="G3" s="784"/>
+      <c r="H3" s="784"/>
+      <c r="I3" s="784"/>
+      <c r="J3" s="784"/>
+      <c r="K3" s="784"/>
+      <c r="L3" s="784"/>
+      <c r="M3" s="784"/>
+      <c r="N3" s="784"/>
+      <c r="O3" s="784"/>
     </row>
     <row r="4" spans="1:17" ht="34.5" customHeight="1">
       <c r="A4" s="752" t="s">
@@ -26682,46 +26691,46 @@
       <c r="O4" s="757"/>
     </row>
     <row r="5" spans="1:17" ht="45.75" customHeight="1">
-      <c r="A5" s="769" t="s">
+      <c r="A5" s="852" t="s">
         <v>970</v>
       </c>
-      <c r="B5" s="769"/>
-      <c r="C5" s="769"/>
-      <c r="D5" s="769"/>
-      <c r="E5" s="769"/>
-      <c r="F5" s="769"/>
-      <c r="G5" s="769"/>
-      <c r="H5" s="769"/>
-      <c r="I5" s="769"/>
-      <c r="J5" s="769"/>
-      <c r="K5" s="769"/>
-      <c r="L5" s="769"/>
-      <c r="M5" s="769"/>
-      <c r="N5" s="769"/>
-      <c r="O5" s="769"/>
+      <c r="B5" s="852"/>
+      <c r="C5" s="852"/>
+      <c r="D5" s="852"/>
+      <c r="E5" s="852"/>
+      <c r="F5" s="852"/>
+      <c r="G5" s="852"/>
+      <c r="H5" s="852"/>
+      <c r="I5" s="852"/>
+      <c r="J5" s="852"/>
+      <c r="K5" s="852"/>
+      <c r="L5" s="852"/>
+      <c r="M5" s="852"/>
+      <c r="N5" s="852"/>
+      <c r="O5" s="852"/>
     </row>
     <row r="6" spans="1:17" ht="30" customHeight="1">
       <c r="A6" s="140"/>
       <c r="B6" s="140"/>
       <c r="C6" s="140"/>
       <c r="D6" s="140"/>
-      <c r="E6" s="765" t="s">
+      <c r="E6" s="767" t="s">
         <v>95</v>
       </c>
-      <c r="F6" s="765"/>
-      <c r="G6" s="765"/>
-      <c r="H6" s="765"/>
+      <c r="F6" s="767"/>
+      <c r="G6" s="767"/>
+      <c r="H6" s="767"/>
       <c r="I6" s="140"/>
-      <c r="J6" s="765" t="s">
+      <c r="J6" s="767" t="s">
         <v>96</v>
       </c>
-      <c r="K6" s="765"/>
-      <c r="L6" s="765"/>
-      <c r="M6" s="765"/>
-      <c r="N6" s="765" t="s">
+      <c r="K6" s="767"/>
+      <c r="L6" s="767"/>
+      <c r="M6" s="767"/>
+      <c r="N6" s="767" t="s">
         <v>103</v>
       </c>
-      <c r="O6" s="765"/>
+      <c r="O6" s="767"/>
     </row>
     <row r="7" spans="1:17" ht="85.5" customHeight="1">
       <c r="A7" s="161"/>
@@ -26765,11 +26774,11 @@
       </c>
     </row>
     <row r="8" spans="1:17" ht="78.75" customHeight="1">
-      <c r="A8" s="766" t="s">
+      <c r="A8" s="850" t="s">
         <v>204</v>
       </c>
-      <c r="B8" s="766"/>
-      <c r="C8" s="766"/>
+      <c r="B8" s="850"/>
+      <c r="C8" s="850"/>
       <c r="D8" s="748" t="s">
         <v>816</v>
       </c>
@@ -26810,11 +26819,11 @@
       </c>
     </row>
     <row r="9" spans="1:17" ht="70.5" customHeight="1">
-      <c r="A9" s="766" t="s">
+      <c r="A9" s="850" t="s">
         <v>752</v>
       </c>
-      <c r="B9" s="766"/>
-      <c r="C9" s="766"/>
+      <c r="B9" s="850"/>
+      <c r="C9" s="850"/>
       <c r="D9" s="748" t="s">
         <v>678</v>
       </c>
@@ -26855,11 +26864,11 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="60.75" customHeight="1">
-      <c r="A10" s="766" t="s">
+      <c r="A10" s="850" t="s">
         <v>751</v>
       </c>
-      <c r="B10" s="766"/>
-      <c r="C10" s="766"/>
+      <c r="B10" s="850"/>
+      <c r="C10" s="850"/>
       <c r="D10" s="751"/>
       <c r="E10" s="177">
         <v>0</v>
@@ -26898,13 +26907,13 @@
       </c>
     </row>
     <row r="11" spans="1:17" ht="69.75" customHeight="1" thickBot="1">
-      <c r="A11" s="764" t="s">
+      <c r="A11" s="849" t="s">
         <v>649</v>
       </c>
-      <c r="B11" s="764" t="s">
+      <c r="B11" s="849" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="764"/>
+      <c r="C11" s="849"/>
       <c r="D11" s="237"/>
       <c r="E11" s="758">
         <f>SUM(E8:E10)</f>
@@ -27042,85 +27051,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="30" customHeight="1">
-      <c r="A1" s="848" t="s">
+      <c r="A1" s="765" t="s">
         <v>408</v>
       </c>
-      <c r="B1" s="848"/>
-      <c r="C1" s="848"/>
-      <c r="D1" s="848"/>
-      <c r="E1" s="848"/>
-      <c r="F1" s="848"/>
-      <c r="G1" s="848"/>
-      <c r="H1" s="848"/>
-      <c r="I1" s="848"/>
-      <c r="J1" s="848"/>
-      <c r="K1" s="848"/>
-      <c r="L1" s="848"/>
-      <c r="M1" s="848"/>
-      <c r="N1" s="848"/>
-      <c r="O1" s="848"/>
-      <c r="P1" s="848"/>
-      <c r="Q1" s="848"/>
-      <c r="R1" s="848"/>
-      <c r="S1" s="848"/>
-      <c r="T1" s="848"/>
-      <c r="U1" s="848"/>
-      <c r="V1" s="848"/>
-      <c r="W1" s="848"/>
+      <c r="B1" s="765"/>
+      <c r="C1" s="765"/>
+      <c r="D1" s="765"/>
+      <c r="E1" s="765"/>
+      <c r="F1" s="765"/>
+      <c r="G1" s="765"/>
+      <c r="H1" s="765"/>
+      <c r="I1" s="765"/>
+      <c r="J1" s="765"/>
+      <c r="K1" s="765"/>
+      <c r="L1" s="765"/>
+      <c r="M1" s="765"/>
+      <c r="N1" s="765"/>
+      <c r="O1" s="765"/>
+      <c r="P1" s="765"/>
+      <c r="Q1" s="765"/>
+      <c r="R1" s="765"/>
+      <c r="S1" s="765"/>
+      <c r="T1" s="765"/>
+      <c r="U1" s="765"/>
+      <c r="V1" s="765"/>
+      <c r="W1" s="765"/>
     </row>
     <row r="2" spans="1:23" ht="30" customHeight="1">
-      <c r="A2" s="849" t="s">
+      <c r="A2" s="766" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="849"/>
-      <c r="C2" s="849"/>
-      <c r="D2" s="849"/>
-      <c r="E2" s="849"/>
-      <c r="F2" s="849"/>
-      <c r="G2" s="849"/>
-      <c r="H2" s="849"/>
-      <c r="I2" s="849"/>
-      <c r="J2" s="849"/>
-      <c r="K2" s="849"/>
-      <c r="L2" s="849"/>
-      <c r="M2" s="849"/>
-      <c r="N2" s="849"/>
-      <c r="O2" s="849"/>
-      <c r="P2" s="849"/>
-      <c r="Q2" s="849"/>
-      <c r="R2" s="849"/>
-      <c r="S2" s="849"/>
-      <c r="T2" s="849"/>
-      <c r="U2" s="849"/>
-      <c r="V2" s="849"/>
-      <c r="W2" s="849"/>
+      <c r="B2" s="766"/>
+      <c r="C2" s="766"/>
+      <c r="D2" s="766"/>
+      <c r="E2" s="766"/>
+      <c r="F2" s="766"/>
+      <c r="G2" s="766"/>
+      <c r="H2" s="766"/>
+      <c r="I2" s="766"/>
+      <c r="J2" s="766"/>
+      <c r="K2" s="766"/>
+      <c r="L2" s="766"/>
+      <c r="M2" s="766"/>
+      <c r="N2" s="766"/>
+      <c r="O2" s="766"/>
+      <c r="P2" s="766"/>
+      <c r="Q2" s="766"/>
+      <c r="R2" s="766"/>
+      <c r="S2" s="766"/>
+      <c r="T2" s="766"/>
+      <c r="U2" s="766"/>
+      <c r="V2" s="766"/>
+      <c r="W2" s="766"/>
     </row>
     <row r="3" spans="1:23" ht="30" customHeight="1">
-      <c r="A3" s="849" t="s">
+      <c r="A3" s="766" t="s">
         <v>605</v>
       </c>
-      <c r="B3" s="849"/>
-      <c r="C3" s="849"/>
-      <c r="D3" s="849"/>
-      <c r="E3" s="849"/>
-      <c r="F3" s="849"/>
-      <c r="G3" s="849"/>
-      <c r="H3" s="849"/>
-      <c r="I3" s="849"/>
-      <c r="J3" s="849"/>
-      <c r="K3" s="849"/>
-      <c r="L3" s="849"/>
-      <c r="M3" s="849"/>
-      <c r="N3" s="849"/>
-      <c r="O3" s="849"/>
-      <c r="P3" s="849"/>
-      <c r="Q3" s="849"/>
-      <c r="R3" s="849"/>
-      <c r="S3" s="849"/>
-      <c r="T3" s="849"/>
-      <c r="U3" s="849"/>
-      <c r="V3" s="849"/>
-      <c r="W3" s="849"/>
+      <c r="B3" s="766"/>
+      <c r="C3" s="766"/>
+      <c r="D3" s="766"/>
+      <c r="E3" s="766"/>
+      <c r="F3" s="766"/>
+      <c r="G3" s="766"/>
+      <c r="H3" s="766"/>
+      <c r="I3" s="766"/>
+      <c r="J3" s="766"/>
+      <c r="K3" s="766"/>
+      <c r="L3" s="766"/>
+      <c r="M3" s="766"/>
+      <c r="N3" s="766"/>
+      <c r="O3" s="766"/>
+      <c r="P3" s="766"/>
+      <c r="Q3" s="766"/>
+      <c r="R3" s="766"/>
+      <c r="S3" s="766"/>
+      <c r="T3" s="766"/>
+      <c r="U3" s="766"/>
+      <c r="V3" s="766"/>
+      <c r="W3" s="766"/>
     </row>
     <row r="4" spans="1:23" ht="30" customHeight="1">
       <c r="A4" s="158">
@@ -27152,62 +27161,62 @@
       <c r="W4" s="153"/>
     </row>
     <row r="5" spans="1:23" ht="43.5" customHeight="1">
-      <c r="A5" s="810" t="s">
+      <c r="A5" s="812" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="810"/>
-      <c r="C5" s="810"/>
-      <c r="D5" s="810"/>
-      <c r="E5" s="810"/>
-      <c r="F5" s="810"/>
-      <c r="G5" s="810"/>
-      <c r="H5" s="810"/>
-      <c r="I5" s="810"/>
-      <c r="J5" s="810"/>
-      <c r="K5" s="810"/>
-      <c r="L5" s="810"/>
-      <c r="M5" s="810"/>
-      <c r="N5" s="810"/>
-      <c r="O5" s="810"/>
-      <c r="P5" s="810"/>
-      <c r="Q5" s="810"/>
-      <c r="R5" s="810"/>
-      <c r="S5" s="810"/>
-      <c r="T5" s="810"/>
-      <c r="U5" s="810"/>
-      <c r="V5" s="810"/>
-      <c r="W5" s="810"/>
+      <c r="B5" s="812"/>
+      <c r="C5" s="812"/>
+      <c r="D5" s="812"/>
+      <c r="E5" s="812"/>
+      <c r="F5" s="812"/>
+      <c r="G5" s="812"/>
+      <c r="H5" s="812"/>
+      <c r="I5" s="812"/>
+      <c r="J5" s="812"/>
+      <c r="K5" s="812"/>
+      <c r="L5" s="812"/>
+      <c r="M5" s="812"/>
+      <c r="N5" s="812"/>
+      <c r="O5" s="812"/>
+      <c r="P5" s="812"/>
+      <c r="Q5" s="812"/>
+      <c r="R5" s="812"/>
+      <c r="S5" s="812"/>
+      <c r="T5" s="812"/>
+      <c r="U5" s="812"/>
+      <c r="V5" s="812"/>
+      <c r="W5" s="812"/>
     </row>
     <row r="6" spans="1:23" ht="30" customHeight="1">
       <c r="A6" s="196"/>
       <c r="B6" s="196"/>
       <c r="C6" s="196"/>
       <c r="D6" s="196"/>
-      <c r="E6" s="765" t="s">
+      <c r="E6" s="767" t="s">
         <v>95</v>
       </c>
-      <c r="F6" s="765"/>
-      <c r="G6" s="765"/>
-      <c r="H6" s="765"/>
-      <c r="I6" s="765"/>
-      <c r="J6" s="765"/>
-      <c r="K6" s="765"/>
+      <c r="F6" s="767"/>
+      <c r="G6" s="767"/>
+      <c r="H6" s="767"/>
+      <c r="I6" s="767"/>
+      <c r="J6" s="767"/>
+      <c r="K6" s="767"/>
       <c r="L6" s="196"/>
-      <c r="M6" s="765" t="s">
+      <c r="M6" s="767" t="s">
         <v>96</v>
       </c>
-      <c r="N6" s="765"/>
-      <c r="O6" s="765"/>
-      <c r="P6" s="765"/>
-      <c r="Q6" s="765"/>
-      <c r="R6" s="765"/>
-      <c r="S6" s="765"/>
+      <c r="N6" s="767"/>
+      <c r="O6" s="767"/>
+      <c r="P6" s="767"/>
+      <c r="Q6" s="767"/>
+      <c r="R6" s="767"/>
+      <c r="S6" s="767"/>
       <c r="T6" s="196"/>
-      <c r="U6" s="765" t="s">
+      <c r="U6" s="767" t="s">
         <v>103</v>
       </c>
-      <c r="V6" s="765"/>
-      <c r="W6" s="765"/>
+      <c r="V6" s="767"/>
+      <c r="W6" s="767"/>
     </row>
     <row r="7" spans="1:23" ht="114">
       <c r="A7" s="140"/>
@@ -27259,11 +27268,11 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="28.5">
-      <c r="A8" s="850" t="s">
+      <c r="A8" s="768" t="s">
         <v>643</v>
       </c>
-      <c r="B8" s="850"/>
-      <c r="C8" s="850"/>
+      <c r="B8" s="768"/>
+      <c r="C8" s="768"/>
       <c r="D8" s="140"/>
       <c r="E8" s="164"/>
       <c r="F8" s="164"/>
@@ -27286,11 +27295,11 @@
       <c r="W8" s="164"/>
     </row>
     <row r="9" spans="1:23" ht="25.5" customHeight="1">
-      <c r="A9" s="852" t="s">
+      <c r="A9" s="770" t="s">
         <v>640</v>
       </c>
-      <c r="B9" s="852"/>
-      <c r="C9" s="852"/>
+      <c r="B9" s="770"/>
+      <c r="C9" s="770"/>
       <c r="D9" s="140"/>
       <c r="E9" s="138">
         <v>6137272530</v>
@@ -27327,11 +27336,11 @@
       </c>
     </row>
     <row r="10" spans="1:23" ht="25.5" customHeight="1">
-      <c r="A10" s="852" t="s">
+      <c r="A10" s="770" t="s">
         <v>641</v>
       </c>
-      <c r="B10" s="852"/>
-      <c r="C10" s="852"/>
+      <c r="B10" s="770"/>
+      <c r="C10" s="770"/>
       <c r="D10" s="140"/>
       <c r="E10" s="138">
         <v>6280866446</v>
@@ -27366,11 +27375,11 @@
       </c>
     </row>
     <row r="11" spans="1:23" ht="25.5" customHeight="1">
-      <c r="A11" s="852" t="s">
+      <c r="A11" s="770" t="s">
         <v>642</v>
       </c>
-      <c r="B11" s="852"/>
-      <c r="C11" s="852"/>
+      <c r="B11" s="770"/>
+      <c r="C11" s="770"/>
       <c r="D11" s="140"/>
       <c r="E11" s="138"/>
       <c r="F11" s="138"/>
@@ -27393,11 +27402,11 @@
       <c r="W11" s="138"/>
     </row>
     <row r="12" spans="1:23" ht="25.5" customHeight="1">
-      <c r="A12" s="852" t="s">
+      <c r="A12" s="770" t="s">
         <v>644</v>
       </c>
-      <c r="B12" s="852"/>
-      <c r="C12" s="852"/>
+      <c r="B12" s="770"/>
+      <c r="C12" s="770"/>
       <c r="D12" s="140"/>
       <c r="E12" s="138"/>
       <c r="F12" s="138"/>
@@ -27420,11 +27429,11 @@
       <c r="W12" s="138"/>
     </row>
     <row r="13" spans="1:23" ht="25.5" customHeight="1">
-      <c r="A13" s="852" t="s">
+      <c r="A13" s="770" t="s">
         <v>645</v>
       </c>
-      <c r="B13" s="852"/>
-      <c r="C13" s="852"/>
+      <c r="B13" s="770"/>
+      <c r="C13" s="770"/>
       <c r="D13" s="140"/>
       <c r="E13" s="138"/>
       <c r="F13" s="138"/>
@@ -27494,11 +27503,11 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27">
-      <c r="A15" s="852" t="s">
+      <c r="A15" s="770" t="s">
         <v>505</v>
       </c>
-      <c r="B15" s="852"/>
-      <c r="C15" s="852"/>
+      <c r="B15" s="770"/>
+      <c r="C15" s="770"/>
       <c r="D15" s="140"/>
       <c r="E15" s="138">
         <v>0</v>
@@ -27566,13 +27575,13 @@
       <c r="W16" s="138"/>
     </row>
     <row r="17" spans="1:23" ht="30" customHeight="1" thickBot="1">
-      <c r="A17" s="810" t="s">
+      <c r="A17" s="812" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="810" t="s">
+      <c r="B17" s="812" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="810"/>
+      <c r="C17" s="812"/>
       <c r="D17" s="140"/>
       <c r="E17" s="168">
         <f>SUM(E8:E16)</f>
@@ -27755,67 +27764,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="30" customHeight="1">
-      <c r="A1" s="848" t="s">
+      <c r="A1" s="765" t="s">
         <v>671</v>
       </c>
-      <c r="B1" s="848"/>
-      <c r="C1" s="848"/>
-      <c r="D1" s="848"/>
-      <c r="E1" s="848"/>
-      <c r="F1" s="848"/>
-      <c r="G1" s="848"/>
-      <c r="H1" s="848"/>
-      <c r="I1" s="848"/>
-      <c r="J1" s="848"/>
-      <c r="K1" s="848"/>
-      <c r="L1" s="848"/>
-      <c r="M1" s="848"/>
-      <c r="N1" s="848"/>
-      <c r="O1" s="848"/>
-      <c r="P1" s="848"/>
-      <c r="Q1" s="848"/>
+      <c r="B1" s="765"/>
+      <c r="C1" s="765"/>
+      <c r="D1" s="765"/>
+      <c r="E1" s="765"/>
+      <c r="F1" s="765"/>
+      <c r="G1" s="765"/>
+      <c r="H1" s="765"/>
+      <c r="I1" s="765"/>
+      <c r="J1" s="765"/>
+      <c r="K1" s="765"/>
+      <c r="L1" s="765"/>
+      <c r="M1" s="765"/>
+      <c r="N1" s="765"/>
+      <c r="O1" s="765"/>
+      <c r="P1" s="765"/>
+      <c r="Q1" s="765"/>
     </row>
     <row r="2" spans="1:17" ht="30" customHeight="1">
-      <c r="A2" s="849" t="s">
+      <c r="A2" s="766" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="849"/>
-      <c r="C2" s="849"/>
-      <c r="D2" s="849"/>
-      <c r="E2" s="849"/>
-      <c r="F2" s="849"/>
-      <c r="G2" s="849"/>
-      <c r="H2" s="849"/>
-      <c r="I2" s="849"/>
-      <c r="J2" s="849"/>
-      <c r="K2" s="849"/>
-      <c r="L2" s="849"/>
-      <c r="M2" s="849"/>
-      <c r="N2" s="849"/>
-      <c r="O2" s="849"/>
-      <c r="P2" s="849"/>
-      <c r="Q2" s="849"/>
+      <c r="B2" s="766"/>
+      <c r="C2" s="766"/>
+      <c r="D2" s="766"/>
+      <c r="E2" s="766"/>
+      <c r="F2" s="766"/>
+      <c r="G2" s="766"/>
+      <c r="H2" s="766"/>
+      <c r="I2" s="766"/>
+      <c r="J2" s="766"/>
+      <c r="K2" s="766"/>
+      <c r="L2" s="766"/>
+      <c r="M2" s="766"/>
+      <c r="N2" s="766"/>
+      <c r="O2" s="766"/>
+      <c r="P2" s="766"/>
+      <c r="Q2" s="766"/>
     </row>
     <row r="3" spans="1:17" ht="30" customHeight="1">
-      <c r="A3" s="849" t="s">
+      <c r="A3" s="766" t="s">
         <v>605</v>
       </c>
-      <c r="B3" s="849"/>
-      <c r="C3" s="849"/>
-      <c r="D3" s="849"/>
-      <c r="E3" s="849"/>
-      <c r="F3" s="849"/>
-      <c r="G3" s="849"/>
-      <c r="H3" s="849"/>
-      <c r="I3" s="849"/>
-      <c r="J3" s="849"/>
-      <c r="K3" s="849"/>
-      <c r="L3" s="849"/>
-      <c r="M3" s="849"/>
-      <c r="N3" s="849"/>
-      <c r="O3" s="849"/>
-      <c r="P3" s="849"/>
-      <c r="Q3" s="849"/>
+      <c r="B3" s="766"/>
+      <c r="C3" s="766"/>
+      <c r="D3" s="766"/>
+      <c r="E3" s="766"/>
+      <c r="F3" s="766"/>
+      <c r="G3" s="766"/>
+      <c r="H3" s="766"/>
+      <c r="I3" s="766"/>
+      <c r="J3" s="766"/>
+      <c r="K3" s="766"/>
+      <c r="L3" s="766"/>
+      <c r="M3" s="766"/>
+      <c r="N3" s="766"/>
+      <c r="O3" s="766"/>
+      <c r="P3" s="766"/>
+      <c r="Q3" s="766"/>
     </row>
     <row r="4" spans="1:17" ht="30" customHeight="1">
       <c r="A4" s="158">
@@ -27841,50 +27850,50 @@
       <c r="Q4" s="153"/>
     </row>
     <row r="5" spans="1:17" ht="43.5" customHeight="1">
-      <c r="A5" s="851" t="s">
+      <c r="A5" s="769" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="851"/>
-      <c r="C5" s="851"/>
-      <c r="D5" s="851"/>
-      <c r="E5" s="851"/>
-      <c r="F5" s="851"/>
-      <c r="G5" s="851"/>
-      <c r="H5" s="851"/>
-      <c r="I5" s="851"/>
-      <c r="J5" s="851"/>
-      <c r="K5" s="851"/>
-      <c r="L5" s="851"/>
-      <c r="M5" s="851"/>
-      <c r="N5" s="851"/>
-      <c r="O5" s="851"/>
-      <c r="P5" s="851"/>
-      <c r="Q5" s="851"/>
+      <c r="B5" s="769"/>
+      <c r="C5" s="769"/>
+      <c r="D5" s="769"/>
+      <c r="E5" s="769"/>
+      <c r="F5" s="769"/>
+      <c r="G5" s="769"/>
+      <c r="H5" s="769"/>
+      <c r="I5" s="769"/>
+      <c r="J5" s="769"/>
+      <c r="K5" s="769"/>
+      <c r="L5" s="769"/>
+      <c r="M5" s="769"/>
+      <c r="N5" s="769"/>
+      <c r="O5" s="769"/>
+      <c r="P5" s="769"/>
+      <c r="Q5" s="769"/>
     </row>
     <row r="6" spans="1:17" ht="30" customHeight="1">
       <c r="A6" s="196"/>
       <c r="B6" s="196"/>
       <c r="C6" s="196"/>
-      <c r="D6" s="765" t="s">
+      <c r="D6" s="767" t="s">
         <v>95</v>
       </c>
-      <c r="E6" s="765"/>
-      <c r="F6" s="765"/>
-      <c r="G6" s="765"/>
-      <c r="H6" s="765"/>
-      <c r="I6" s="765"/>
+      <c r="E6" s="767"/>
+      <c r="F6" s="767"/>
+      <c r="G6" s="767"/>
+      <c r="H6" s="767"/>
+      <c r="I6" s="767"/>
       <c r="J6" s="196"/>
-      <c r="K6" s="765" t="s">
+      <c r="K6" s="767" t="s">
         <v>96</v>
       </c>
-      <c r="L6" s="765"/>
-      <c r="M6" s="765"/>
-      <c r="N6" s="765"/>
-      <c r="O6" s="765"/>
-      <c r="P6" s="765" t="s">
+      <c r="L6" s="767"/>
+      <c r="M6" s="767"/>
+      <c r="N6" s="767"/>
+      <c r="O6" s="767"/>
+      <c r="P6" s="767" t="s">
         <v>103</v>
       </c>
-      <c r="Q6" s="765"/>
+      <c r="Q6" s="767"/>
     </row>
     <row r="7" spans="1:17" ht="90">
       <c r="A7" s="140"/>
@@ -27934,11 +27943,11 @@
       </c>
     </row>
     <row r="8" spans="1:17" ht="28.5">
-      <c r="A8" s="850" t="s">
+      <c r="A8" s="768" t="s">
         <v>643</v>
       </c>
-      <c r="B8" s="850"/>
-      <c r="C8" s="850"/>
+      <c r="B8" s="768"/>
+      <c r="C8" s="768"/>
       <c r="D8" s="138">
         <v>0</v>
       </c>
@@ -27977,11 +27986,11 @@
       </c>
     </row>
     <row r="9" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A9" s="852" t="s">
+      <c r="A9" s="770" t="s">
         <v>642</v>
       </c>
-      <c r="B9" s="852"/>
-      <c r="C9" s="852"/>
+      <c r="B9" s="770"/>
+      <c r="C9" s="770"/>
       <c r="D9" s="138">
         <v>0</v>
       </c>
@@ -28025,11 +28034,11 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A10" s="852" t="s">
+      <c r="A10" s="770" t="s">
         <v>640</v>
       </c>
-      <c r="B10" s="852"/>
-      <c r="C10" s="852"/>
+      <c r="B10" s="770"/>
+      <c r="C10" s="770"/>
       <c r="D10" s="138">
         <v>6137272530</v>
       </c>
@@ -28075,11 +28084,11 @@
       </c>
     </row>
     <row r="11" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A11" s="852" t="s">
+      <c r="A11" s="770" t="s">
         <v>647</v>
       </c>
-      <c r="B11" s="852"/>
-      <c r="C11" s="852"/>
+      <c r="B11" s="770"/>
+      <c r="C11" s="770"/>
       <c r="D11" s="138">
         <v>6280866446</v>
       </c>
@@ -28123,11 +28132,11 @@
       </c>
     </row>
     <row r="12" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A12" s="852" t="s">
+      <c r="A12" s="770" t="s">
         <v>645</v>
       </c>
-      <c r="B12" s="852"/>
-      <c r="C12" s="852"/>
+      <c r="B12" s="770"/>
+      <c r="C12" s="770"/>
       <c r="D12" s="138">
         <v>0</v>
       </c>
@@ -28213,11 +28222,11 @@
       </c>
     </row>
     <row r="14" spans="1:17" ht="27" hidden="1">
-      <c r="A14" s="852" t="s">
+      <c r="A14" s="770" t="s">
         <v>505</v>
       </c>
-      <c r="B14" s="852"/>
-      <c r="C14" s="852"/>
+      <c r="B14" s="770"/>
+      <c r="C14" s="770"/>
       <c r="D14" s="138">
         <v>0</v>
       </c>
@@ -28273,13 +28282,13 @@
       <c r="Q15" s="138"/>
     </row>
     <row r="16" spans="1:17" ht="30" customHeight="1" thickBot="1">
-      <c r="A16" s="851" t="s">
+      <c r="A16" s="769" t="s">
         <v>649</v>
       </c>
-      <c r="B16" s="851" t="s">
+      <c r="B16" s="769" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="851"/>
+      <c r="C16" s="769"/>
       <c r="D16" s="208">
         <f t="shared" ref="D16:I16" si="4">SUM(D8:D15)</f>
         <v>29558707742</v>
@@ -28385,26 +28394,26 @@
       <c r="A19" s="196"/>
       <c r="B19" s="196"/>
       <c r="C19" s="196"/>
-      <c r="D19" s="765" t="s">
+      <c r="D19" s="767" t="s">
         <v>95</v>
       </c>
-      <c r="E19" s="765"/>
-      <c r="F19" s="765"/>
-      <c r="G19" s="765"/>
-      <c r="H19" s="765"/>
-      <c r="I19" s="765"/>
+      <c r="E19" s="767"/>
+      <c r="F19" s="767"/>
+      <c r="G19" s="767"/>
+      <c r="H19" s="767"/>
+      <c r="I19" s="767"/>
       <c r="J19" s="196"/>
-      <c r="K19" s="765" t="s">
+      <c r="K19" s="767" t="s">
         <v>96</v>
       </c>
-      <c r="L19" s="765"/>
-      <c r="M19" s="765"/>
-      <c r="N19" s="765"/>
-      <c r="O19" s="765"/>
-      <c r="P19" s="765" t="s">
+      <c r="L19" s="767"/>
+      <c r="M19" s="767"/>
+      <c r="N19" s="767"/>
+      <c r="O19" s="767"/>
+      <c r="P19" s="767" t="s">
         <v>103</v>
       </c>
-      <c r="Q19" s="765"/>
+      <c r="Q19" s="767"/>
     </row>
     <row r="20" spans="1:17" ht="90">
       <c r="A20" s="161"/>
@@ -28454,11 +28463,11 @@
       </c>
     </row>
     <row r="21" spans="1:17" ht="30" customHeight="1">
-      <c r="A21" s="852" t="s">
+      <c r="A21" s="770" t="s">
         <v>648</v>
       </c>
-      <c r="B21" s="852"/>
-      <c r="C21" s="852"/>
+      <c r="B21" s="770"/>
+      <c r="C21" s="770"/>
       <c r="D21" s="223">
         <v>0</v>
       </c>
@@ -28494,11 +28503,11 @@
       </c>
     </row>
     <row r="22" spans="1:17" ht="30" customHeight="1">
-      <c r="A22" s="852" t="s">
+      <c r="A22" s="770" t="s">
         <v>499</v>
       </c>
-      <c r="B22" s="852"/>
-      <c r="C22" s="852"/>
+      <c r="B22" s="770"/>
+      <c r="C22" s="770"/>
       <c r="D22" s="177">
         <v>31854000</v>
       </c>
@@ -28536,11 +28545,11 @@
       </c>
     </row>
     <row r="23" spans="1:17" ht="30" customHeight="1">
-      <c r="A23" s="852" t="s">
+      <c r="A23" s="770" t="s">
         <v>553</v>
       </c>
-      <c r="B23" s="852"/>
-      <c r="C23" s="852"/>
+      <c r="B23" s="770"/>
+      <c r="C23" s="770"/>
       <c r="D23" s="177">
         <v>7120000</v>
       </c>
@@ -28576,11 +28585,11 @@
       </c>
     </row>
     <row r="24" spans="1:17" ht="30" customHeight="1">
-      <c r="A24" s="852" t="s">
+      <c r="A24" s="770" t="s">
         <v>650</v>
       </c>
-      <c r="B24" s="852"/>
-      <c r="C24" s="852"/>
+      <c r="B24" s="770"/>
+      <c r="C24" s="770"/>
       <c r="D24" s="220">
         <v>0</v>
       </c>
@@ -28616,11 +28625,11 @@
       </c>
     </row>
     <row r="25" spans="1:17" ht="30" customHeight="1">
-      <c r="A25" s="852" t="s">
+      <c r="A25" s="770" t="s">
         <v>204</v>
       </c>
-      <c r="B25" s="852"/>
-      <c r="C25" s="852"/>
+      <c r="B25" s="770"/>
+      <c r="C25" s="770"/>
       <c r="D25" s="177">
         <v>32700000</v>
       </c>
@@ -28662,13 +28671,13 @@
       </c>
     </row>
     <row r="26" spans="1:17" ht="30" customHeight="1" thickBot="1">
-      <c r="A26" s="851" t="s">
+      <c r="A26" s="769" t="s">
         <v>649</v>
       </c>
-      <c r="B26" s="851" t="s">
+      <c r="B26" s="769" t="s">
         <v>101</v>
       </c>
-      <c r="C26" s="851"/>
+      <c r="C26" s="769"/>
       <c r="D26" s="208">
         <f t="shared" ref="D26:I26" si="6">SUM(D21:D25)</f>
         <v>71674000</v>
@@ -28852,67 +28861,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1">
-      <c r="A1" s="848" t="s">
+      <c r="A1" s="765" t="s">
         <v>408</v>
       </c>
-      <c r="B1" s="848"/>
-      <c r="C1" s="848"/>
-      <c r="D1" s="848"/>
-      <c r="E1" s="848"/>
-      <c r="F1" s="848"/>
-      <c r="G1" s="848"/>
-      <c r="H1" s="848"/>
-      <c r="I1" s="848"/>
-      <c r="J1" s="848"/>
-      <c r="K1" s="848"/>
-      <c r="L1" s="848"/>
-      <c r="M1" s="848"/>
-      <c r="N1" s="848"/>
-      <c r="O1" s="848"/>
-      <c r="P1" s="848"/>
-      <c r="Q1" s="848"/>
+      <c r="B1" s="765"/>
+      <c r="C1" s="765"/>
+      <c r="D1" s="765"/>
+      <c r="E1" s="765"/>
+      <c r="F1" s="765"/>
+      <c r="G1" s="765"/>
+      <c r="H1" s="765"/>
+      <c r="I1" s="765"/>
+      <c r="J1" s="765"/>
+      <c r="K1" s="765"/>
+      <c r="L1" s="765"/>
+      <c r="M1" s="765"/>
+      <c r="N1" s="765"/>
+      <c r="O1" s="765"/>
+      <c r="P1" s="765"/>
+      <c r="Q1" s="765"/>
     </row>
     <row r="2" spans="1:19" ht="30" customHeight="1">
-      <c r="A2" s="849" t="s">
+      <c r="A2" s="766" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="849"/>
-      <c r="C2" s="849"/>
-      <c r="D2" s="849"/>
-      <c r="E2" s="849"/>
-      <c r="F2" s="849"/>
-      <c r="G2" s="849"/>
-      <c r="H2" s="849"/>
-      <c r="I2" s="849"/>
-      <c r="J2" s="849"/>
-      <c r="K2" s="849"/>
-      <c r="L2" s="849"/>
-      <c r="M2" s="849"/>
-      <c r="N2" s="849"/>
-      <c r="O2" s="849"/>
-      <c r="P2" s="849"/>
-      <c r="Q2" s="849"/>
+      <c r="B2" s="766"/>
+      <c r="C2" s="766"/>
+      <c r="D2" s="766"/>
+      <c r="E2" s="766"/>
+      <c r="F2" s="766"/>
+      <c r="G2" s="766"/>
+      <c r="H2" s="766"/>
+      <c r="I2" s="766"/>
+      <c r="J2" s="766"/>
+      <c r="K2" s="766"/>
+      <c r="L2" s="766"/>
+      <c r="M2" s="766"/>
+      <c r="N2" s="766"/>
+      <c r="O2" s="766"/>
+      <c r="P2" s="766"/>
+      <c r="Q2" s="766"/>
     </row>
     <row r="3" spans="1:19" ht="30" customHeight="1">
-      <c r="A3" s="849" t="s">
+      <c r="A3" s="766" t="s">
         <v>605</v>
       </c>
-      <c r="B3" s="849"/>
-      <c r="C3" s="849"/>
-      <c r="D3" s="849"/>
-      <c r="E3" s="849"/>
-      <c r="F3" s="849"/>
-      <c r="G3" s="849"/>
-      <c r="H3" s="849"/>
-      <c r="I3" s="849"/>
-      <c r="J3" s="849"/>
-      <c r="K3" s="849"/>
-      <c r="L3" s="849"/>
-      <c r="M3" s="849"/>
-      <c r="N3" s="849"/>
-      <c r="O3" s="849"/>
-      <c r="P3" s="849"/>
-      <c r="Q3" s="849"/>
+      <c r="B3" s="766"/>
+      <c r="C3" s="766"/>
+      <c r="D3" s="766"/>
+      <c r="E3" s="766"/>
+      <c r="F3" s="766"/>
+      <c r="G3" s="766"/>
+      <c r="H3" s="766"/>
+      <c r="I3" s="766"/>
+      <c r="J3" s="766"/>
+      <c r="K3" s="766"/>
+      <c r="L3" s="766"/>
+      <c r="M3" s="766"/>
+      <c r="N3" s="766"/>
+      <c r="O3" s="766"/>
+      <c r="P3" s="766"/>
+      <c r="Q3" s="766"/>
     </row>
     <row r="4" spans="1:19" ht="30" customHeight="1">
       <c r="A4" s="268" t="s">
@@ -28936,50 +28945,50 @@
       <c r="Q4" s="153"/>
     </row>
     <row r="5" spans="1:19" ht="43.5" customHeight="1">
-      <c r="A5" s="851" t="s">
+      <c r="A5" s="769" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="851"/>
-      <c r="C5" s="851"/>
-      <c r="D5" s="851"/>
-      <c r="E5" s="851"/>
-      <c r="F5" s="851"/>
-      <c r="G5" s="851"/>
-      <c r="H5" s="851"/>
-      <c r="I5" s="851"/>
-      <c r="J5" s="851"/>
-      <c r="K5" s="851"/>
-      <c r="L5" s="851"/>
-      <c r="M5" s="851"/>
-      <c r="N5" s="851"/>
-      <c r="O5" s="851"/>
-      <c r="P5" s="851"/>
-      <c r="Q5" s="851"/>
+      <c r="B5" s="769"/>
+      <c r="C5" s="769"/>
+      <c r="D5" s="769"/>
+      <c r="E5" s="769"/>
+      <c r="F5" s="769"/>
+      <c r="G5" s="769"/>
+      <c r="H5" s="769"/>
+      <c r="I5" s="769"/>
+      <c r="J5" s="769"/>
+      <c r="K5" s="769"/>
+      <c r="L5" s="769"/>
+      <c r="M5" s="769"/>
+      <c r="N5" s="769"/>
+      <c r="O5" s="769"/>
+      <c r="P5" s="769"/>
+      <c r="Q5" s="769"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="196"/>
       <c r="B6" s="196"/>
       <c r="C6" s="196"/>
       <c r="D6" s="196"/>
-      <c r="E6" s="765" t="s">
+      <c r="E6" s="767" t="s">
         <v>95</v>
       </c>
-      <c r="F6" s="765"/>
-      <c r="G6" s="765"/>
-      <c r="H6" s="765"/>
-      <c r="I6" s="765"/>
+      <c r="F6" s="767"/>
+      <c r="G6" s="767"/>
+      <c r="H6" s="767"/>
+      <c r="I6" s="767"/>
       <c r="J6" s="196"/>
-      <c r="K6" s="765" t="s">
+      <c r="K6" s="767" t="s">
         <v>96</v>
       </c>
-      <c r="L6" s="765"/>
-      <c r="M6" s="765"/>
-      <c r="N6" s="765"/>
-      <c r="O6" s="765"/>
-      <c r="P6" s="765" t="s">
+      <c r="L6" s="767"/>
+      <c r="M6" s="767"/>
+      <c r="N6" s="767"/>
+      <c r="O6" s="767"/>
+      <c r="P6" s="767" t="s">
         <v>103</v>
       </c>
-      <c r="Q6" s="765"/>
+      <c r="Q6" s="767"/>
     </row>
     <row r="7" spans="1:19" ht="60" customHeight="1">
       <c r="A7" s="140"/>
@@ -29029,11 +29038,11 @@
       </c>
     </row>
     <row r="8" spans="1:19" ht="33" customHeight="1">
-      <c r="A8" s="850" t="s">
+      <c r="A8" s="768" t="s">
         <v>643</v>
       </c>
-      <c r="B8" s="850"/>
-      <c r="C8" s="850"/>
+      <c r="B8" s="768"/>
+      <c r="C8" s="768"/>
       <c r="D8" s="140" t="s">
         <v>495</v>
       </c>
@@ -29075,11 +29084,11 @@
       </c>
     </row>
     <row r="9" spans="1:19" ht="33" customHeight="1">
-      <c r="A9" s="852" t="s">
+      <c r="A9" s="770" t="s">
         <v>642</v>
       </c>
-      <c r="B9" s="852"/>
-      <c r="C9" s="852"/>
+      <c r="B9" s="770"/>
+      <c r="C9" s="770"/>
       <c r="D9" s="247" t="s">
         <v>496</v>
       </c>
@@ -29126,11 +29135,11 @@
       </c>
     </row>
     <row r="10" spans="1:19" ht="33" customHeight="1">
-      <c r="A10" s="852" t="s">
+      <c r="A10" s="770" t="s">
         <v>640</v>
       </c>
-      <c r="B10" s="852"/>
-      <c r="C10" s="852"/>
+      <c r="B10" s="770"/>
+      <c r="C10" s="770"/>
       <c r="D10" s="247" t="s">
         <v>663</v>
       </c>
@@ -29177,11 +29186,11 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="33" customHeight="1">
-      <c r="A11" s="852" t="s">
+      <c r="A11" s="770" t="s">
         <v>647</v>
       </c>
-      <c r="B11" s="852"/>
-      <c r="C11" s="852"/>
+      <c r="B11" s="770"/>
+      <c r="C11" s="770"/>
       <c r="D11" s="247" t="s">
         <v>664</v>
       </c>
@@ -29228,11 +29237,11 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="33" customHeight="1">
-      <c r="A12" s="852" t="s">
+      <c r="A12" s="770" t="s">
         <v>645</v>
       </c>
-      <c r="B12" s="852"/>
-      <c r="C12" s="852"/>
+      <c r="B12" s="770"/>
+      <c r="C12" s="770"/>
       <c r="D12" s="247" t="s">
         <v>669</v>
       </c>
@@ -29324,13 +29333,13 @@
       </c>
     </row>
     <row r="14" spans="1:19" ht="37.5" customHeight="1" thickBot="1">
-      <c r="A14" s="764" t="s">
+      <c r="A14" s="849" t="s">
         <v>649</v>
       </c>
-      <c r="B14" s="764" t="s">
+      <c r="B14" s="849" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="764"/>
+      <c r="C14" s="849"/>
       <c r="D14" s="237"/>
       <c r="E14" s="238">
         <f>SUM(E8:E13)</f>
@@ -29430,25 +29439,25 @@
       <c r="B17" s="196"/>
       <c r="C17" s="196"/>
       <c r="D17" s="196"/>
-      <c r="E17" s="765" t="s">
+      <c r="E17" s="767" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="765"/>
-      <c r="G17" s="765"/>
-      <c r="H17" s="765"/>
-      <c r="I17" s="765"/>
+      <c r="F17" s="767"/>
+      <c r="G17" s="767"/>
+      <c r="H17" s="767"/>
+      <c r="I17" s="767"/>
       <c r="J17" s="196"/>
-      <c r="K17" s="765" t="s">
+      <c r="K17" s="767" t="s">
         <v>96</v>
       </c>
-      <c r="L17" s="765"/>
-      <c r="M17" s="765"/>
-      <c r="N17" s="765"/>
-      <c r="O17" s="765"/>
-      <c r="P17" s="765" t="s">
+      <c r="L17" s="767"/>
+      <c r="M17" s="767"/>
+      <c r="N17" s="767"/>
+      <c r="O17" s="767"/>
+      <c r="P17" s="767" t="s">
         <v>103</v>
       </c>
-      <c r="Q17" s="765"/>
+      <c r="Q17" s="767"/>
     </row>
     <row r="18" spans="1:19" ht="78" customHeight="1">
       <c r="A18" s="161"/>
@@ -29498,11 +29507,11 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="39.75" customHeight="1">
-      <c r="A19" s="852" t="s">
+      <c r="A19" s="770" t="s">
         <v>204</v>
       </c>
-      <c r="B19" s="852"/>
-      <c r="C19" s="852"/>
+      <c r="B19" s="770"/>
+      <c r="C19" s="770"/>
       <c r="D19" s="206"/>
       <c r="E19" s="247">
         <v>32700000</v>
@@ -29543,13 +29552,13 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="37.5" customHeight="1" thickBot="1">
-      <c r="A20" s="764" t="s">
+      <c r="A20" s="849" t="s">
         <v>649</v>
       </c>
-      <c r="B20" s="764" t="s">
+      <c r="B20" s="849" t="s">
         <v>101</v>
       </c>
-      <c r="C20" s="764"/>
+      <c r="C20" s="849"/>
       <c r="D20" s="237"/>
       <c r="E20" s="238">
         <f>SUM(E19:E19)</f>
@@ -29641,11 +29650,11 @@
       <c r="P25" s="200"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
-      <c r="A26" s="852" t="s">
+      <c r="A26" s="770" t="s">
         <v>648</v>
       </c>
-      <c r="B26" s="852"/>
-      <c r="C26" s="852"/>
+      <c r="B26" s="770"/>
+      <c r="C26" s="770"/>
       <c r="D26" s="206"/>
       <c r="E26" s="267">
         <v>0</v>
@@ -29678,11 +29687,11 @@
       </c>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
-      <c r="A27" s="852" t="s">
+      <c r="A27" s="770" t="s">
         <v>499</v>
       </c>
-      <c r="B27" s="852"/>
-      <c r="C27" s="852"/>
+      <c r="B27" s="770"/>
+      <c r="C27" s="770"/>
       <c r="D27" s="206"/>
       <c r="E27" s="247">
         <v>31854000</v>
@@ -29717,11 +29726,11 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
-      <c r="A28" s="852" t="s">
+      <c r="A28" s="770" t="s">
         <v>553</v>
       </c>
-      <c r="B28" s="852"/>
-      <c r="C28" s="852"/>
+      <c r="B28" s="770"/>
+      <c r="C28" s="770"/>
       <c r="D28" s="206"/>
       <c r="E28" s="247">
         <v>7120000</v>
@@ -29754,11 +29763,11 @@
       </c>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
-      <c r="A29" s="852" t="s">
+      <c r="A29" s="770" t="s">
         <v>650</v>
       </c>
-      <c r="B29" s="852"/>
-      <c r="C29" s="852"/>
+      <c r="B29" s="770"/>
+      <c r="C29" s="770"/>
       <c r="D29" s="206"/>
       <c r="E29" s="221">
         <v>0</v>
@@ -30323,7 +30332,7 @@
     <col min="12" max="12" width="0.85546875" style="136" customWidth="1"/>
     <col min="13" max="13" width="17.7109375" style="136" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="0.85546875" style="136" customWidth="1"/>
-    <col min="15" max="15" width="16.85546875" style="136" customWidth="1"/>
+    <col min="15" max="15" width="18.28515625" style="136" customWidth="1"/>
     <col min="16" max="16" width="14.42578125" style="136" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="1" style="136" customWidth="1"/>
     <col min="18" max="18" width="10.85546875" style="136" bestFit="1" customWidth="1"/>
@@ -30346,61 +30355,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="25.5">
-      <c r="A1" s="772" t="s">
+      <c r="A1" s="773" t="s">
         <v>960</v>
       </c>
-      <c r="B1" s="772"/>
-      <c r="C1" s="772"/>
-      <c r="D1" s="772"/>
-      <c r="E1" s="772"/>
-      <c r="F1" s="772"/>
-      <c r="G1" s="772"/>
-      <c r="H1" s="772"/>
-      <c r="I1" s="772"/>
-      <c r="J1" s="772"/>
-      <c r="K1" s="772"/>
-      <c r="L1" s="772"/>
-      <c r="M1" s="772"/>
-      <c r="N1" s="772"/>
-      <c r="O1" s="772"/>
+      <c r="B1" s="773"/>
+      <c r="C1" s="773"/>
+      <c r="D1" s="773"/>
+      <c r="E1" s="773"/>
+      <c r="F1" s="773"/>
+      <c r="G1" s="773"/>
+      <c r="H1" s="773"/>
+      <c r="I1" s="773"/>
+      <c r="J1" s="773"/>
+      <c r="K1" s="773"/>
+      <c r="L1" s="773"/>
+      <c r="M1" s="773"/>
+      <c r="N1" s="773"/>
+      <c r="O1" s="773"/>
     </row>
     <row r="2" spans="1:18" ht="25.5">
-      <c r="A2" s="772" t="s">
+      <c r="A2" s="773" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="772"/>
-      <c r="C2" s="772"/>
-      <c r="D2" s="772"/>
-      <c r="E2" s="772"/>
-      <c r="F2" s="772"/>
-      <c r="G2" s="772"/>
-      <c r="H2" s="772"/>
-      <c r="I2" s="772"/>
-      <c r="J2" s="772"/>
-      <c r="K2" s="772"/>
-      <c r="L2" s="772"/>
-      <c r="M2" s="772"/>
-      <c r="N2" s="772"/>
-      <c r="O2" s="772"/>
+      <c r="B2" s="773"/>
+      <c r="C2" s="773"/>
+      <c r="D2" s="773"/>
+      <c r="E2" s="773"/>
+      <c r="F2" s="773"/>
+      <c r="G2" s="773"/>
+      <c r="H2" s="773"/>
+      <c r="I2" s="773"/>
+      <c r="J2" s="773"/>
+      <c r="K2" s="773"/>
+      <c r="L2" s="773"/>
+      <c r="M2" s="773"/>
+      <c r="N2" s="773"/>
+      <c r="O2" s="773"/>
     </row>
     <row r="3" spans="1:18" ht="25.5">
-      <c r="A3" s="772" t="s">
+      <c r="A3" s="773" t="s">
         <v>721</v>
       </c>
-      <c r="B3" s="772"/>
-      <c r="C3" s="772"/>
-      <c r="D3" s="772"/>
-      <c r="E3" s="772"/>
-      <c r="F3" s="772"/>
-      <c r="G3" s="772"/>
-      <c r="H3" s="772"/>
-      <c r="I3" s="772"/>
-      <c r="J3" s="772"/>
-      <c r="K3" s="772"/>
-      <c r="L3" s="772"/>
-      <c r="M3" s="772"/>
-      <c r="N3" s="772"/>
-      <c r="O3" s="772"/>
+      <c r="B3" s="773"/>
+      <c r="C3" s="773"/>
+      <c r="D3" s="773"/>
+      <c r="E3" s="773"/>
+      <c r="F3" s="773"/>
+      <c r="G3" s="773"/>
+      <c r="H3" s="773"/>
+      <c r="I3" s="773"/>
+      <c r="J3" s="773"/>
+      <c r="K3" s="773"/>
+      <c r="L3" s="773"/>
+      <c r="M3" s="773"/>
+      <c r="N3" s="773"/>
+      <c r="O3" s="773"/>
     </row>
     <row r="4" spans="1:18" ht="21">
       <c r="A4" s="392"/>
@@ -30408,11 +30417,11 @@
       <c r="C4" s="392"/>
       <c r="D4" s="392"/>
       <c r="E4" s="393"/>
-      <c r="F4" s="773" t="s">
+      <c r="F4" s="774" t="s">
         <v>637</v>
       </c>
-      <c r="G4" s="773"/>
-      <c r="H4" s="773"/>
+      <c r="G4" s="774"/>
+      <c r="H4" s="774"/>
       <c r="I4" s="392"/>
       <c r="J4" s="392"/>
       <c r="K4" s="392"/>
@@ -30501,7 +30510,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="400"/>
-      <c r="E8" s="393">
+      <c r="E8" s="915">
         <f>يادداشتها!F12</f>
         <v>110234473507</v>
       </c>
@@ -30522,7 +30531,7 @@
         <v>12</v>
       </c>
       <c r="L8" s="400"/>
-      <c r="M8" s="393">
+      <c r="M8" s="915">
         <f>يادداشتها!F226</f>
         <v>12057773251</v>
       </c>
@@ -30588,7 +30597,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="400"/>
-      <c r="E10" s="393">
+      <c r="E10" s="915">
         <f>يادداشتها!F94</f>
         <v>10149042108</v>
       </c>
@@ -30729,7 +30738,7 @@
         <v>15</v>
       </c>
       <c r="L14" s="400"/>
-      <c r="M14" s="393">
+      <c r="M14" s="915">
         <f>يادداشتها!F283</f>
         <v>24569309765</v>
       </c>
@@ -30751,7 +30760,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="400"/>
-      <c r="E15" s="393">
+      <c r="E15" s="915">
         <f>'دارایی ثابت مشهود'!N16</f>
         <v>930623919515</v>
       </c>
@@ -30793,7 +30802,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="400"/>
-      <c r="E16" s="393">
+      <c r="E16" s="915">
         <f>'دارایی نامشهود'!N11</f>
         <v>32387008784</v>
       </c>
@@ -30833,7 +30842,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="400"/>
-      <c r="E17" s="393">
+      <c r="E17" s="915">
         <f>يادداشتها!F200</f>
         <v>25301169258</v>
       </c>
@@ -30917,7 +30926,7 @@
         <v>1125357598540</v>
       </c>
       <c r="N19" s="400"/>
-      <c r="O19" s="393">
+      <c r="O19" s="915">
         <f>ع!I31</f>
         <v>992674152405.85938</v>
       </c>
@@ -30990,84 +30999,84 @@
     </row>
     <row r="22" spans="1:44" ht="22.5" customHeight="1" thickTop="1"/>
     <row r="23" spans="1:44" ht="22.5" customHeight="1">
-      <c r="A23" s="774" t="s">
+      <c r="A23" s="775" t="s">
         <v>386</v>
       </c>
-      <c r="B23" s="774"/>
-      <c r="C23" s="774"/>
-      <c r="D23" s="774"/>
-      <c r="E23" s="774"/>
-      <c r="F23" s="774"/>
-      <c r="G23" s="774"/>
-      <c r="H23" s="774"/>
-      <c r="I23" s="774"/>
-      <c r="J23" s="774"/>
-      <c r="K23" s="774"/>
-      <c r="L23" s="774"/>
-      <c r="M23" s="774"/>
-      <c r="N23" s="774"/>
-      <c r="O23" s="774"/>
+      <c r="B23" s="775"/>
+      <c r="C23" s="775"/>
+      <c r="D23" s="775"/>
+      <c r="E23" s="775"/>
+      <c r="F23" s="775"/>
+      <c r="G23" s="775"/>
+      <c r="H23" s="775"/>
+      <c r="I23" s="775"/>
+      <c r="J23" s="775"/>
+      <c r="K23" s="775"/>
+      <c r="L23" s="775"/>
+      <c r="M23" s="775"/>
+      <c r="N23" s="775"/>
+      <c r="O23" s="775"/>
     </row>
     <row r="24" spans="1:44" s="21" customFormat="1" ht="32.25">
-      <c r="A24" s="775" t="s">
+      <c r="A24" s="776" t="s">
         <v>145</v>
       </c>
-      <c r="B24" s="775"/>
-      <c r="C24" s="775"/>
-      <c r="D24" s="775"/>
-      <c r="E24" s="775"/>
+      <c r="B24" s="776"/>
+      <c r="C24" s="776"/>
+      <c r="D24" s="776"/>
+      <c r="E24" s="776"/>
       <c r="F24" s="406"/>
       <c r="G24" s="407"/>
-      <c r="H24" s="776" t="s">
+      <c r="H24" s="777" t="s">
         <v>127</v>
       </c>
-      <c r="I24" s="776"/>
-      <c r="J24" s="776"/>
-      <c r="K24" s="776"/>
-      <c r="L24" s="776"/>
-      <c r="M24" s="776"/>
+      <c r="I24" s="777"/>
+      <c r="J24" s="777"/>
+      <c r="K24" s="777"/>
+      <c r="L24" s="777"/>
+      <c r="M24" s="777"/>
       <c r="N24" s="149"/>
       <c r="O24" s="149"/>
     </row>
     <row r="25" spans="1:44" ht="25.5">
-      <c r="A25" s="775" t="s">
+      <c r="A25" s="776" t="s">
         <v>128</v>
       </c>
-      <c r="B25" s="775"/>
-      <c r="C25" s="775"/>
-      <c r="D25" s="775"/>
-      <c r="E25" s="775"/>
+      <c r="B25" s="776"/>
+      <c r="C25" s="776"/>
+      <c r="D25" s="776"/>
+      <c r="E25" s="776"/>
       <c r="F25" s="398"/>
       <c r="G25" s="398"/>
       <c r="H25" s="398"/>
-      <c r="I25" s="776" t="s">
+      <c r="I25" s="777" t="s">
         <v>581</v>
       </c>
-      <c r="J25" s="776"/>
-      <c r="K25" s="776"/>
-      <c r="L25" s="776"/>
-      <c r="M25" s="776"/>
+      <c r="J25" s="777"/>
+      <c r="K25" s="777"/>
+      <c r="L25" s="777"/>
+      <c r="M25" s="777"/>
       <c r="N25" s="398"/>
       <c r="O25" s="398"/>
     </row>
     <row r="26" spans="1:44" ht="42.75" customHeight="1">
-      <c r="A26" s="777">
+      <c r="A26" s="778">
         <v>2</v>
       </c>
-      <c r="B26" s="777"/>
-      <c r="C26" s="777"/>
-      <c r="D26" s="777"/>
-      <c r="E26" s="777"/>
-      <c r="F26" s="777"/>
-      <c r="G26" s="777"/>
-      <c r="H26" s="777"/>
-      <c r="I26" s="777"/>
-      <c r="J26" s="777"/>
-      <c r="K26" s="777"/>
-      <c r="L26" s="777"/>
-      <c r="M26" s="777"/>
-      <c r="N26" s="777"/>
-      <c r="O26" s="777"/>
+      <c r="B26" s="778"/>
+      <c r="C26" s="778"/>
+      <c r="D26" s="778"/>
+      <c r="E26" s="778"/>
+      <c r="F26" s="778"/>
+      <c r="G26" s="778"/>
+      <c r="H26" s="778"/>
+      <c r="I26" s="778"/>
+      <c r="J26" s="778"/>
+      <c r="K26" s="778"/>
+      <c r="L26" s="778"/>
+      <c r="M26" s="778"/>
+      <c r="N26" s="778"/>
+      <c r="O26" s="778"/>
     </row>
     <row r="27" spans="1:44" ht="24">
       <c r="I27" s="156">
@@ -31110,7 +31119,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.19685039370078741" top="0.31496062992125984" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="87" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -35292,7 +35301,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="B3:B5"/>
@@ -35312,6 +35320,7 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A19:B19"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.19685039370078741" top="0.35433070866141736" bottom="0.43307086614173229" header="0.59055118110236227" footer="0.19685039370078741"/>
@@ -36135,47 +36144,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="22.5">
-      <c r="A1" s="778" t="s">
+      <c r="A1" s="779" t="s">
         <v>960</v>
       </c>
-      <c r="B1" s="778"/>
-      <c r="C1" s="778"/>
-      <c r="D1" s="778"/>
-      <c r="E1" s="778"/>
-      <c r="F1" s="778"/>
-      <c r="G1" s="778"/>
-      <c r="H1" s="778"/>
-      <c r="I1" s="778"/>
+      <c r="B1" s="779"/>
+      <c r="C1" s="779"/>
+      <c r="D1" s="779"/>
+      <c r="E1" s="779"/>
+      <c r="F1" s="779"/>
+      <c r="G1" s="779"/>
+      <c r="H1" s="779"/>
+      <c r="I1" s="779"/>
       <c r="J1" s="178"/>
       <c r="K1" s="178"/>
     </row>
     <row r="2" spans="1:11" ht="22.5">
-      <c r="A2" s="778" t="s">
+      <c r="A2" s="779" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="778"/>
-      <c r="C2" s="778"/>
-      <c r="D2" s="778"/>
-      <c r="E2" s="778"/>
-      <c r="F2" s="778"/>
-      <c r="G2" s="778"/>
-      <c r="H2" s="778"/>
-      <c r="I2" s="778"/>
+      <c r="B2" s="779"/>
+      <c r="C2" s="779"/>
+      <c r="D2" s="779"/>
+      <c r="E2" s="779"/>
+      <c r="F2" s="779"/>
+      <c r="G2" s="779"/>
+      <c r="H2" s="779"/>
+      <c r="I2" s="779"/>
       <c r="J2" s="178"/>
       <c r="K2" s="178"/>
     </row>
     <row r="3" spans="1:11" ht="22.5">
-      <c r="A3" s="778" t="s">
+      <c r="A3" s="779" t="s">
         <v>723</v>
       </c>
-      <c r="B3" s="778"/>
-      <c r="C3" s="778"/>
-      <c r="D3" s="778"/>
-      <c r="E3" s="778"/>
-      <c r="F3" s="778"/>
-      <c r="G3" s="778"/>
-      <c r="H3" s="778"/>
-      <c r="I3" s="778"/>
+      <c r="B3" s="779"/>
+      <c r="C3" s="779"/>
+      <c r="D3" s="779"/>
+      <c r="E3" s="779"/>
+      <c r="F3" s="779"/>
+      <c r="G3" s="779"/>
+      <c r="H3" s="779"/>
+      <c r="I3" s="779"/>
       <c r="J3" s="178"/>
       <c r="K3" s="178"/>
     </row>
@@ -36201,11 +36210,11 @@
         <v>70</v>
       </c>
       <c r="D5" s="398"/>
-      <c r="E5" s="780" t="s">
+      <c r="E5" s="781" t="s">
         <v>722</v>
       </c>
-      <c r="F5" s="781"/>
-      <c r="G5" s="780"/>
+      <c r="F5" s="782"/>
+      <c r="G5" s="781"/>
       <c r="H5" s="398"/>
       <c r="I5" s="397" t="s">
         <v>601</v>
@@ -36236,7 +36245,7 @@
       <c r="C8" s="400">
         <v>17</v>
       </c>
-      <c r="E8" s="552">
+      <c r="E8" s="916">
         <f>يادداشتها!F301</f>
         <v>175005286000</v>
       </c>
@@ -36272,7 +36281,7 @@
       <c r="C10" s="400">
         <v>19</v>
       </c>
-      <c r="E10" s="552">
+      <c r="E10" s="916">
         <f>يادداشتها!F336</f>
         <v>30660000000</v>
       </c>
@@ -36401,7 +36410,7 @@
       </c>
       <c r="C18" s="400"/>
       <c r="E18" s="135"/>
-      <c r="G18" s="340">
+      <c r="G18" s="917">
         <f>SUM(E13:E17)</f>
         <v>-150027736305</v>
       </c>
@@ -36425,7 +36434,7 @@
       <c r="C20" s="400">
         <v>25</v>
       </c>
-      <c r="E20" s="552">
+      <c r="E20" s="916">
         <f>يادداشتها!F416</f>
         <v>78732076442</v>
       </c>
@@ -36442,7 +36451,7 @@
       <c r="C21" s="400">
         <v>26</v>
       </c>
-      <c r="E21" s="340">
+      <c r="E21" s="917">
         <f>-'درآمد دولت'!C5</f>
         <v>-56206000000</v>
       </c>
@@ -36485,17 +36494,17 @@
       <c r="I24" s="398"/>
     </row>
     <row r="25" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A25" s="778" t="s">
+      <c r="A25" s="779" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="778"/>
-      <c r="C25" s="778"/>
-      <c r="D25" s="778"/>
-      <c r="E25" s="778"/>
-      <c r="F25" s="778"/>
-      <c r="G25" s="778"/>
-      <c r="H25" s="778"/>
-      <c r="I25" s="778"/>
+      <c r="B25" s="779"/>
+      <c r="C25" s="779"/>
+      <c r="D25" s="779"/>
+      <c r="E25" s="779"/>
+      <c r="F25" s="779"/>
+      <c r="G25" s="779"/>
+      <c r="H25" s="779"/>
+      <c r="I25" s="779"/>
     </row>
     <row r="26" spans="1:11" ht="19.5" customHeight="1">
       <c r="A26" s="401" t="s">
@@ -36619,17 +36628,17 @@
     </row>
     <row r="32" spans="1:11" ht="19.5" customHeight="1" thickTop="1"/>
     <row r="33" spans="1:22" ht="19.5">
-      <c r="A33" s="774" t="s">
+      <c r="A33" s="775" t="s">
         <v>386</v>
       </c>
-      <c r="B33" s="774"/>
-      <c r="C33" s="774"/>
-      <c r="D33" s="774"/>
-      <c r="E33" s="774"/>
-      <c r="F33" s="774"/>
-      <c r="G33" s="774"/>
-      <c r="H33" s="774"/>
-      <c r="I33" s="774"/>
+      <c r="B33" s="775"/>
+      <c r="C33" s="775"/>
+      <c r="D33" s="775"/>
+      <c r="E33" s="775"/>
+      <c r="F33" s="775"/>
+      <c r="G33" s="775"/>
+      <c r="H33" s="775"/>
+      <c r="I33" s="775"/>
     </row>
     <row r="34" spans="1:22" s="21" customFormat="1" ht="32.25">
       <c r="A34" s="411" t="s">
@@ -36659,11 +36668,11 @@
       <c r="D35" s="414"/>
       <c r="E35" s="414"/>
       <c r="F35" s="398"/>
-      <c r="G35" s="776" t="s">
+      <c r="G35" s="777" t="s">
         <v>581</v>
       </c>
-      <c r="H35" s="776"/>
-      <c r="I35" s="776"/>
+      <c r="H35" s="777"/>
+      <c r="I35" s="777"/>
       <c r="J35" s="181"/>
       <c r="K35" s="181"/>
       <c r="L35" s="181"/>
@@ -36672,17 +36681,17 @@
       <c r="O35" s="174"/>
     </row>
     <row r="36" spans="1:22" ht="33.75" customHeight="1">
-      <c r="A36" s="779">
+      <c r="A36" s="780">
         <v>3</v>
       </c>
-      <c r="B36" s="779"/>
-      <c r="C36" s="779"/>
-      <c r="D36" s="779"/>
-      <c r="E36" s="779"/>
-      <c r="F36" s="779"/>
-      <c r="G36" s="779"/>
-      <c r="H36" s="779"/>
-      <c r="I36" s="779"/>
+      <c r="B36" s="780"/>
+      <c r="C36" s="780"/>
+      <c r="D36" s="780"/>
+      <c r="E36" s="780"/>
+      <c r="F36" s="780"/>
+      <c r="G36" s="780"/>
+      <c r="H36" s="780"/>
+      <c r="I36" s="780"/>
       <c r="J36" s="182"/>
       <c r="K36" s="183"/>
       <c r="L36" s="183"/>
@@ -38459,51 +38468,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="128" customFormat="1" ht="24" customHeight="1">
-      <c r="A1" s="783" t="s">
+      <c r="A1" s="785" t="s">
         <v>960</v>
       </c>
-      <c r="B1" s="783"/>
-      <c r="C1" s="783"/>
-      <c r="D1" s="783"/>
-      <c r="E1" s="783"/>
-      <c r="F1" s="783"/>
-      <c r="G1" s="783"/>
-      <c r="H1" s="783"/>
-      <c r="I1" s="783"/>
-      <c r="J1" s="783"/>
-      <c r="K1" s="783"/>
+      <c r="B1" s="785"/>
+      <c r="C1" s="785"/>
+      <c r="D1" s="785"/>
+      <c r="E1" s="785"/>
+      <c r="F1" s="785"/>
+      <c r="G1" s="785"/>
+      <c r="H1" s="785"/>
+      <c r="I1" s="785"/>
+      <c r="J1" s="785"/>
+      <c r="K1" s="785"/>
       <c r="L1" s="260"/>
     </row>
     <row r="2" spans="1:17" s="128" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A2" s="783" t="s">
+      <c r="A2" s="785" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="783"/>
-      <c r="C2" s="783"/>
-      <c r="D2" s="783"/>
-      <c r="E2" s="783"/>
-      <c r="F2" s="783"/>
-      <c r="G2" s="783"/>
-      <c r="H2" s="783"/>
-      <c r="I2" s="783"/>
-      <c r="J2" s="783"/>
-      <c r="K2" s="783"/>
+      <c r="B2" s="785"/>
+      <c r="C2" s="785"/>
+      <c r="D2" s="785"/>
+      <c r="E2" s="785"/>
+      <c r="F2" s="785"/>
+      <c r="G2" s="785"/>
+      <c r="H2" s="785"/>
+      <c r="I2" s="785"/>
+      <c r="J2" s="785"/>
+      <c r="K2" s="785"/>
       <c r="L2" s="260"/>
     </row>
     <row r="3" spans="1:17" s="128" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A3" s="783" t="s">
+      <c r="A3" s="785" t="s">
         <v>724</v>
       </c>
-      <c r="B3" s="783"/>
-      <c r="C3" s="783"/>
-      <c r="D3" s="783"/>
-      <c r="E3" s="783"/>
-      <c r="F3" s="783"/>
-      <c r="G3" s="783"/>
-      <c r="H3" s="783"/>
-      <c r="I3" s="783"/>
-      <c r="J3" s="783"/>
-      <c r="K3" s="783"/>
+      <c r="B3" s="785"/>
+      <c r="C3" s="785"/>
+      <c r="D3" s="785"/>
+      <c r="E3" s="785"/>
+      <c r="F3" s="785"/>
+      <c r="G3" s="785"/>
+      <c r="H3" s="785"/>
+      <c r="I3" s="785"/>
+      <c r="J3" s="785"/>
+      <c r="K3" s="785"/>
       <c r="L3" s="260"/>
     </row>
     <row r="4" spans="1:17" ht="12.75" customHeight="1">
@@ -38523,11 +38532,11 @@
     <row r="5" spans="1:17" ht="25.5">
       <c r="B5" s="596"/>
       <c r="C5" s="596"/>
-      <c r="D5" s="784" t="s">
+      <c r="D5" s="786" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="784"/>
-      <c r="F5" s="784"/>
+      <c r="E5" s="786"/>
+      <c r="F5" s="786"/>
       <c r="G5" s="597"/>
       <c r="H5" s="598" t="s">
         <v>965</v>
@@ -38585,7 +38594,7 @@
       <c r="A8" s="417" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="786" t="s">
+      <c r="B8" s="788" t="s">
         <v>506</v>
       </c>
       <c r="C8" s="604"/>
@@ -38604,7 +38613,7 @@
       <c r="A9" s="219" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="786"/>
+      <c r="B9" s="788"/>
       <c r="C9" s="219"/>
       <c r="D9" s="605">
         <f>' مصوب'!E6+'وجوه مصرف نشده'!H7+'وجوه مصرف نشده'!H9+'سايرمنابع جاری'!D18</f>
@@ -38637,7 +38646,7 @@
       <c r="A10" s="219" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="786"/>
+      <c r="B10" s="788"/>
       <c r="C10" s="219"/>
       <c r="D10" s="605">
         <f>' مصوب'!C10+'وجوه مصرف نشده'!C17</f>
@@ -38669,7 +38678,7 @@
       <c r="A11" s="219" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="786"/>
+      <c r="B11" s="788"/>
       <c r="C11" s="219"/>
       <c r="D11" s="605">
         <f>' مصوب'!C14+'وجوه مصرف نشده'!H19+'وجوه مصرف نشده'!H24</f>
@@ -38742,7 +38751,7 @@
       <c r="A14" s="417" t="s">
         <v>80</v>
       </c>
-      <c r="B14" s="786" t="s">
+      <c r="B14" s="788" t="s">
         <v>507</v>
       </c>
       <c r="C14" s="129"/>
@@ -38758,7 +38767,7 @@
       <c r="A15" s="219" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="786"/>
+      <c r="B15" s="788"/>
       <c r="D15" s="605">
         <f>D9</f>
         <v>165155772833</v>
@@ -38788,7 +38797,7 @@
       <c r="A16" s="219" t="s">
         <v>82</v>
       </c>
-      <c r="B16" s="786"/>
+      <c r="B16" s="788"/>
       <c r="D16" s="605">
         <f>D10</f>
         <v>43490149047.040001</v>
@@ -38818,7 +38827,7 @@
       <c r="A17" s="219" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="786"/>
+      <c r="B17" s="788"/>
       <c r="D17" s="605">
         <f>D11</f>
         <v>33071116623</v>
@@ -38910,41 +38919,41 @@
       <c r="F21" s="334"/>
     </row>
     <row r="22" spans="1:13" s="219" customFormat="1" ht="27">
-      <c r="A22" s="785" t="s">
+      <c r="A22" s="787" t="s">
         <v>428</v>
       </c>
-      <c r="B22" s="785"/>
-      <c r="C22" s="785"/>
-      <c r="D22" s="785"/>
-      <c r="E22" s="785"/>
-      <c r="F22" s="785"/>
-      <c r="G22" s="785"/>
-      <c r="H22" s="785"/>
-      <c r="I22" s="785"/>
-      <c r="J22" s="785"/>
+      <c r="B22" s="787"/>
+      <c r="C22" s="787"/>
+      <c r="D22" s="787"/>
+      <c r="E22" s="787"/>
+      <c r="F22" s="787"/>
+      <c r="G22" s="787"/>
+      <c r="H22" s="787"/>
+      <c r="I22" s="787"/>
+      <c r="J22" s="787"/>
     </row>
     <row r="23" spans="1:13" s="416" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A23" s="782" t="s">
+      <c r="A23" s="783" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="782"/>
+      <c r="B23" s="783"/>
       <c r="D23" s="419"/>
       <c r="E23" s="415"/>
       <c r="F23" s="419"/>
-      <c r="G23" s="782" t="s">
+      <c r="G23" s="783" t="s">
         <v>401</v>
       </c>
-      <c r="H23" s="782"/>
+      <c r="H23" s="783"/>
       <c r="I23" s="415"/>
       <c r="J23" s="415"/>
       <c r="L23" s="418"/>
       <c r="M23" s="418"/>
     </row>
     <row r="24" spans="1:13" s="416" customFormat="1" ht="36" customHeight="1">
-      <c r="A24" s="782" t="s">
+      <c r="A24" s="783" t="s">
         <v>128</v>
       </c>
-      <c r="B24" s="782"/>
+      <c r="B24" s="783"/>
       <c r="D24" s="419"/>
       <c r="E24" s="415"/>
       <c r="F24" s="419"/>
@@ -38958,13 +38967,13 @@
       <c r="M24" s="418"/>
     </row>
     <row r="25" spans="1:13" s="416" customFormat="1" ht="32.25">
-      <c r="B25" s="768">
+      <c r="B25" s="784">
         <v>4</v>
       </c>
-      <c r="C25" s="768"/>
-      <c r="D25" s="768"/>
-      <c r="E25" s="768"/>
-      <c r="F25" s="768"/>
+      <c r="C25" s="784"/>
+      <c r="D25" s="784"/>
+      <c r="E25" s="784"/>
+      <c r="F25" s="784"/>
       <c r="G25" s="419"/>
       <c r="H25" s="419"/>
       <c r="I25" s="419"/>
@@ -39040,43 +39049,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="139" customFormat="1" ht="32.25">
-      <c r="A1" s="787" t="s">
+      <c r="A1" s="789" t="s">
         <v>960</v>
       </c>
-      <c r="B1" s="787"/>
-      <c r="C1" s="787"/>
-      <c r="D1" s="787"/>
-      <c r="E1" s="787"/>
-      <c r="F1" s="787"/>
-      <c r="G1" s="787"/>
-      <c r="H1" s="787"/>
-      <c r="I1" s="787"/>
+      <c r="B1" s="789"/>
+      <c r="C1" s="789"/>
+      <c r="D1" s="789"/>
+      <c r="E1" s="789"/>
+      <c r="F1" s="789"/>
+      <c r="G1" s="789"/>
+      <c r="H1" s="789"/>
+      <c r="I1" s="789"/>
     </row>
     <row r="2" spans="1:12" s="139" customFormat="1" ht="32.25">
-      <c r="A2" s="787" t="s">
+      <c r="A2" s="789" t="s">
         <v>536</v>
       </c>
-      <c r="B2" s="787"/>
-      <c r="C2" s="787"/>
-      <c r="D2" s="787"/>
-      <c r="E2" s="787"/>
-      <c r="F2" s="787"/>
-      <c r="G2" s="787"/>
-      <c r="H2" s="787"/>
-      <c r="I2" s="787"/>
+      <c r="B2" s="789"/>
+      <c r="C2" s="789"/>
+      <c r="D2" s="789"/>
+      <c r="E2" s="789"/>
+      <c r="F2" s="789"/>
+      <c r="G2" s="789"/>
+      <c r="H2" s="789"/>
+      <c r="I2" s="789"/>
     </row>
     <row r="3" spans="1:12" s="139" customFormat="1" ht="32.25">
-      <c r="A3" s="787" t="s">
+      <c r="A3" s="789" t="s">
         <v>725</v>
       </c>
-      <c r="B3" s="787"/>
-      <c r="C3" s="787"/>
-      <c r="D3" s="787"/>
-      <c r="E3" s="787"/>
-      <c r="F3" s="787"/>
-      <c r="G3" s="787"/>
-      <c r="H3" s="787"/>
-      <c r="I3" s="787"/>
+      <c r="B3" s="789"/>
+      <c r="C3" s="789"/>
+      <c r="D3" s="789"/>
+      <c r="E3" s="789"/>
+      <c r="F3" s="789"/>
+      <c r="G3" s="789"/>
+      <c r="H3" s="789"/>
+      <c r="I3" s="789"/>
     </row>
     <row r="4" spans="1:12" s="139" customFormat="1" ht="32.25">
       <c r="A4" s="421"/>
@@ -39122,16 +39131,16 @@
       <c r="A7" s="617"/>
       <c r="B7" s="617"/>
       <c r="C7" s="617"/>
-      <c r="D7" s="793"/>
-      <c r="E7" s="794" t="s">
+      <c r="D7" s="795"/>
+      <c r="E7" s="796" t="s">
         <v>92</v>
       </c>
       <c r="F7" s="322"/>
-      <c r="G7" s="788" t="s">
+      <c r="G7" s="790" t="s">
         <v>106</v>
       </c>
       <c r="H7" s="643"/>
-      <c r="I7" s="788" t="s">
+      <c r="I7" s="790" t="s">
         <v>107</v>
       </c>
     </row>
@@ -39139,12 +39148,12 @@
       <c r="A8" s="617"/>
       <c r="B8" s="617"/>
       <c r="C8" s="617"/>
-      <c r="D8" s="793"/>
-      <c r="E8" s="795"/>
+      <c r="D8" s="795"/>
+      <c r="E8" s="797"/>
       <c r="F8" s="618"/>
-      <c r="G8" s="789"/>
+      <c r="G8" s="791"/>
       <c r="H8" s="618"/>
-      <c r="I8" s="789"/>
+      <c r="I8" s="791"/>
     </row>
     <row r="9" spans="1:12" s="427" customFormat="1" ht="18" customHeight="1">
       <c r="A9" s="617"/>
@@ -39328,15 +39337,15 @@
       <c r="B17" s="617"/>
       <c r="C17" s="617"/>
       <c r="D17" s="617"/>
-      <c r="E17" s="797" t="s">
+      <c r="E17" s="799" t="s">
         <v>92</v>
       </c>
       <c r="F17" s="626"/>
-      <c r="G17" s="790" t="s">
+      <c r="G17" s="792" t="s">
         <v>106</v>
       </c>
       <c r="H17" s="626"/>
-      <c r="I17" s="790" t="s">
+      <c r="I17" s="792" t="s">
         <v>107</v>
       </c>
     </row>
@@ -39347,18 +39356,18 @@
       </c>
       <c r="C18" s="617"/>
       <c r="D18" s="617"/>
-      <c r="E18" s="798"/>
+      <c r="E18" s="800"/>
       <c r="F18" s="415"/>
-      <c r="G18" s="791"/>
+      <c r="G18" s="793"/>
       <c r="H18" s="415"/>
-      <c r="I18" s="791"/>
+      <c r="I18" s="793"/>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1">
-      <c r="A19" s="792" t="s">
+      <c r="A19" s="794" t="s">
         <v>114</v>
       </c>
-      <c r="B19" s="792"/>
-      <c r="C19" s="792"/>
+      <c r="B19" s="794"/>
+      <c r="C19" s="794"/>
       <c r="D19" s="623"/>
       <c r="E19" s="637"/>
       <c r="F19" s="326"/>
@@ -39516,11 +39525,11 @@
       <c r="M26" s="15"/>
     </row>
     <row r="27" spans="1:14" ht="18" customHeight="1">
-      <c r="A27" s="792" t="s">
+      <c r="A27" s="794" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="792"/>
-      <c r="C27" s="792"/>
+      <c r="B27" s="794"/>
+      <c r="C27" s="794"/>
       <c r="D27" s="623"/>
       <c r="E27" s="615"/>
       <c r="F27" s="323"/>
@@ -40069,11 +40078,11 @@
       <c r="M51" s="15"/>
     </row>
     <row r="52" spans="1:13" ht="18" customHeight="1">
-      <c r="A52" s="792" t="s">
+      <c r="A52" s="794" t="s">
         <v>396</v>
       </c>
-      <c r="B52" s="792"/>
-      <c r="C52" s="792"/>
+      <c r="B52" s="794"/>
+      <c r="C52" s="794"/>
       <c r="D52" s="623"/>
       <c r="E52" s="615"/>
       <c r="F52" s="323"/>
@@ -40085,10 +40094,10 @@
     </row>
     <row r="53" spans="1:13" ht="18" customHeight="1">
       <c r="A53" s="376"/>
-      <c r="B53" s="796" t="s">
+      <c r="B53" s="798" t="s">
         <v>347</v>
       </c>
-      <c r="C53" s="796"/>
+      <c r="C53" s="798"/>
       <c r="D53" s="623"/>
       <c r="E53" s="615">
         <v>4000000000</v>
@@ -40107,11 +40116,11 @@
       <c r="M53" s="15"/>
     </row>
     <row r="54" spans="1:13" ht="18" customHeight="1">
-      <c r="A54" s="792" t="s">
+      <c r="A54" s="794" t="s">
         <v>493</v>
       </c>
-      <c r="B54" s="792"/>
-      <c r="C54" s="792"/>
+      <c r="B54" s="794"/>
+      <c r="C54" s="794"/>
       <c r="D54" s="623"/>
       <c r="E54" s="615"/>
       <c r="F54" s="323"/>
@@ -40435,39 +40444,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="139" customFormat="1" ht="32.25">
-      <c r="A1" s="787" t="s">
+      <c r="A1" s="789" t="s">
         <v>960</v>
       </c>
-      <c r="B1" s="787"/>
-      <c r="C1" s="787"/>
-      <c r="D1" s="787"/>
-      <c r="E1" s="787"/>
+      <c r="B1" s="789"/>
+      <c r="C1" s="789"/>
+      <c r="D1" s="789"/>
+      <c r="E1" s="789"/>
       <c r="F1" s="697"/>
       <c r="G1" s="697"/>
       <c r="H1" s="697"/>
       <c r="I1" s="697"/>
     </row>
     <row r="2" spans="1:9" s="139" customFormat="1" ht="32.25">
-      <c r="A2" s="787" t="s">
+      <c r="A2" s="789" t="s">
         <v>536</v>
       </c>
-      <c r="B2" s="787"/>
-      <c r="C2" s="787"/>
-      <c r="D2" s="787"/>
-      <c r="E2" s="787"/>
+      <c r="B2" s="789"/>
+      <c r="C2" s="789"/>
+      <c r="D2" s="789"/>
+      <c r="E2" s="789"/>
       <c r="F2" s="697"/>
       <c r="G2" s="697"/>
       <c r="H2" s="697"/>
       <c r="I2" s="697"/>
     </row>
     <row r="3" spans="1:9" s="139" customFormat="1" ht="32.25">
-      <c r="A3" s="787" t="s">
+      <c r="A3" s="789" t="s">
         <v>725</v>
       </c>
-      <c r="B3" s="787"/>
-      <c r="C3" s="787"/>
-      <c r="D3" s="787"/>
-      <c r="E3" s="787"/>
+      <c r="B3" s="789"/>
+      <c r="C3" s="789"/>
+      <c r="D3" s="789"/>
+      <c r="E3" s="789"/>
       <c r="F3" s="697"/>
       <c r="G3" s="697"/>
       <c r="H3" s="697"/>
@@ -40477,22 +40486,22 @@
       <c r="A4" s="641" t="s">
         <v>964</v>
       </c>
-      <c r="B4" s="799" t="s">
+      <c r="B4" s="801" t="s">
         <v>868</v>
       </c>
-      <c r="C4" s="799"/>
-      <c r="D4" s="799"/>
-      <c r="E4" s="799"/>
+      <c r="C4" s="801"/>
+      <c r="D4" s="801"/>
+      <c r="E4" s="801"/>
       <c r="F4" s="676"/>
       <c r="G4" s="676"/>
       <c r="H4" s="676"/>
     </row>
     <row r="5" spans="1:9" ht="41.25" customHeight="1">
       <c r="A5" s="641"/>
-      <c r="B5" s="799"/>
-      <c r="C5" s="799"/>
-      <c r="D5" s="799"/>
-      <c r="E5" s="799"/>
+      <c r="B5" s="801"/>
+      <c r="C5" s="801"/>
+      <c r="D5" s="801"/>
+      <c r="E5" s="801"/>
       <c r="F5" s="676"/>
       <c r="G5" s="676"/>
       <c r="H5" s="676"/>
@@ -41625,38 +41634,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" s="706" customFormat="1">
-      <c r="B2" s="800" t="s">
+      <c r="B2" s="802" t="s">
         <v>636</v>
       </c>
-      <c r="C2" s="801" t="s">
+      <c r="C2" s="803" t="s">
         <v>635</v>
       </c>
-      <c r="D2" s="802" t="s">
+      <c r="D2" s="804" t="s">
         <v>634</v>
       </c>
-      <c r="E2" s="803" t="s">
+      <c r="E2" s="805" t="s">
         <v>589</v>
       </c>
-      <c r="F2" s="803"/>
-      <c r="G2" s="802" t="s">
+      <c r="F2" s="805"/>
+      <c r="G2" s="804" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="3" spans="2:8" s="708" customFormat="1" ht="24.75">
-      <c r="B3" s="800"/>
-      <c r="C3" s="801"/>
-      <c r="D3" s="802"/>
+      <c r="B3" s="802"/>
+      <c r="C3" s="803"/>
+      <c r="D3" s="804"/>
       <c r="E3" s="707" t="s">
         <v>633</v>
       </c>
       <c r="F3" s="707" t="s">
         <v>632</v>
       </c>
-      <c r="G3" s="802"/>
+      <c r="G3" s="804"/>
     </row>
     <row r="4" spans="2:8" s="708" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B4" s="800"/>
-      <c r="C4" s="801"/>
+      <c r="B4" s="802"/>
+      <c r="C4" s="803"/>
       <c r="D4" s="709" t="s">
         <v>42</v>
       </c>
@@ -41826,40 +41835,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.5">
-      <c r="A1" s="810" t="s">
+      <c r="A1" s="812" t="s">
         <v>960</v>
       </c>
-      <c r="B1" s="810"/>
-      <c r="C1" s="810"/>
-      <c r="D1" s="810"/>
-      <c r="E1" s="810"/>
-      <c r="F1" s="810"/>
-      <c r="G1" s="810"/>
-      <c r="H1" s="810"/>
+      <c r="B1" s="812"/>
+      <c r="C1" s="812"/>
+      <c r="D1" s="812"/>
+      <c r="E1" s="812"/>
+      <c r="F1" s="812"/>
+      <c r="G1" s="812"/>
+      <c r="H1" s="812"/>
     </row>
     <row r="2" spans="1:12" ht="28.5">
-      <c r="A2" s="810" t="s">
+      <c r="A2" s="812" t="s">
         <v>536</v>
       </c>
-      <c r="B2" s="810"/>
-      <c r="C2" s="810"/>
-      <c r="D2" s="810"/>
-      <c r="E2" s="810"/>
-      <c r="F2" s="810"/>
-      <c r="G2" s="810"/>
-      <c r="H2" s="810"/>
+      <c r="B2" s="812"/>
+      <c r="C2" s="812"/>
+      <c r="D2" s="812"/>
+      <c r="E2" s="812"/>
+      <c r="F2" s="812"/>
+      <c r="G2" s="812"/>
+      <c r="H2" s="812"/>
     </row>
     <row r="3" spans="1:12" ht="28.5">
-      <c r="A3" s="810" t="s">
+      <c r="A3" s="812" t="s">
         <v>712</v>
       </c>
-      <c r="B3" s="810"/>
-      <c r="C3" s="810"/>
-      <c r="D3" s="810"/>
-      <c r="E3" s="810"/>
-      <c r="F3" s="810"/>
-      <c r="G3" s="810"/>
-      <c r="H3" s="810"/>
+      <c r="B3" s="812"/>
+      <c r="C3" s="812"/>
+      <c r="D3" s="812"/>
+      <c r="E3" s="812"/>
+      <c r="F3" s="812"/>
+      <c r="G3" s="812"/>
+      <c r="H3" s="812"/>
     </row>
     <row r="4" spans="1:12" ht="33.75" customHeight="1">
       <c r="A4" s="358" t="s">
@@ -42354,15 +42363,15 @@
       <c r="A31" s="698" t="s">
         <v>944</v>
       </c>
-      <c r="B31" s="815" t="s">
+      <c r="B31" s="816" t="s">
         <v>946</v>
       </c>
-      <c r="C31" s="815"/>
-      <c r="D31" s="815"/>
-      <c r="E31" s="815"/>
-      <c r="F31" s="815"/>
-      <c r="G31" s="815"/>
-      <c r="H31" s="815"/>
+      <c r="C31" s="816"/>
+      <c r="D31" s="816"/>
+      <c r="E31" s="816"/>
+      <c r="F31" s="816"/>
+      <c r="G31" s="816"/>
+      <c r="H31" s="816"/>
       <c r="I31" s="156"/>
       <c r="J31" s="156"/>
     </row>
@@ -43317,7 +43326,7 @@
         <v>845</v>
       </c>
       <c r="C92" s="383"/>
-      <c r="D92" s="816" t="s">
+      <c r="D92" s="817" t="s">
         <v>847</v>
       </c>
       <c r="E92" s="385"/>
@@ -43335,7 +43344,7 @@
         <v>846</v>
       </c>
       <c r="C93" s="383"/>
-      <c r="D93" s="816"/>
+      <c r="D93" s="817"/>
       <c r="E93" s="385"/>
       <c r="F93" s="247">
         <v>356140566</v>
@@ -43380,15 +43389,15 @@
       <c r="A96" s="747" t="s">
         <v>847</v>
       </c>
-      <c r="B96" s="819" t="s">
+      <c r="B96" s="820" t="s">
         <v>967</v>
       </c>
-      <c r="C96" s="819"/>
-      <c r="D96" s="819"/>
-      <c r="E96" s="819"/>
-      <c r="F96" s="819"/>
-      <c r="G96" s="819"/>
-      <c r="H96" s="819"/>
+      <c r="C96" s="820"/>
+      <c r="D96" s="820"/>
+      <c r="E96" s="820"/>
+      <c r="F96" s="820"/>
+      <c r="G96" s="820"/>
+      <c r="H96" s="820"/>
       <c r="I96" s="33"/>
     </row>
     <row r="97" spans="1:10" ht="30.75" customHeight="1">
@@ -43563,7 +43572,7 @@
         <v>183</v>
       </c>
       <c r="C108" s="139"/>
-      <c r="D108" s="813" t="s">
+      <c r="D108" s="814" t="s">
         <v>957</v>
       </c>
       <c r="E108" s="138"/>
@@ -43581,7 +43590,7 @@
         <v>184</v>
       </c>
       <c r="C109" s="139"/>
-      <c r="D109" s="813"/>
+      <c r="D109" s="814"/>
       <c r="E109" s="138"/>
       <c r="F109" s="138">
         <f>'مانده پرداختهای غیر قطعی سن'!E6</f>
@@ -43598,7 +43607,7 @@
         <v>185</v>
       </c>
       <c r="C110" s="139"/>
-      <c r="D110" s="813"/>
+      <c r="D110" s="814"/>
       <c r="E110" s="138"/>
       <c r="F110" s="138">
         <f>'مانده پرداختهای غیر قطعی سن'!E16</f>
@@ -43686,7 +43695,7 @@
         <v>187</v>
       </c>
       <c r="C116" s="139"/>
-      <c r="D116" s="813" t="s">
+      <c r="D116" s="814" t="s">
         <v>957</v>
       </c>
       <c r="E116" s="138"/>
@@ -43704,7 +43713,7 @@
         <v>188</v>
       </c>
       <c r="C117" s="139"/>
-      <c r="D117" s="813"/>
+      <c r="D117" s="814"/>
       <c r="E117" s="138"/>
       <c r="F117" s="138">
         <f>'مانده پرداختهای غیر قطعی سن'!E22</f>
@@ -43774,16 +43783,16 @@
       <c r="D129" s="244"/>
     </row>
     <row r="130" spans="1:10">
-      <c r="A130" s="814" t="s">
+      <c r="A130" s="815" t="s">
         <v>515</v>
       </c>
-      <c r="B130" s="814"/>
-      <c r="C130" s="814"/>
-      <c r="D130" s="814"/>
-      <c r="E130" s="814"/>
-      <c r="F130" s="814"/>
-      <c r="G130" s="814"/>
-      <c r="H130" s="814"/>
+      <c r="B130" s="815"/>
+      <c r="C130" s="815"/>
+      <c r="D130" s="815"/>
+      <c r="E130" s="815"/>
+      <c r="F130" s="815"/>
+      <c r="G130" s="815"/>
+      <c r="H130" s="815"/>
     </row>
     <row r="131" spans="1:10" s="36" customFormat="1" ht="22.5" customHeight="1">
       <c r="A131" s="158">
@@ -43849,7 +43858,7 @@
         <v>657</v>
       </c>
       <c r="C135" s="362"/>
-      <c r="D135" s="805" t="s">
+      <c r="D135" s="807" t="s">
         <v>676</v>
       </c>
       <c r="E135" s="138"/>
@@ -43866,7 +43875,7 @@
         <v>658</v>
       </c>
       <c r="C136" s="362"/>
-      <c r="D136" s="805"/>
+      <c r="D136" s="807"/>
       <c r="E136" s="138"/>
       <c r="F136" s="247">
         <v>21000000000</v>
@@ -43882,7 +43891,7 @@
         <v>659</v>
       </c>
       <c r="C137" s="362"/>
-      <c r="D137" s="805"/>
+      <c r="D137" s="807"/>
       <c r="E137" s="138"/>
       <c r="F137" s="247">
         <v>200000000000</v>
@@ -43897,7 +43906,7 @@
         <v>660</v>
       </c>
       <c r="C138" s="362"/>
-      <c r="D138" s="805"/>
+      <c r="D138" s="807"/>
       <c r="E138" s="138"/>
       <c r="F138" s="247">
         <v>10050000000</v>
@@ -43982,7 +43991,7 @@
         <v>692</v>
       </c>
       <c r="C144" s="362"/>
-      <c r="D144" s="805"/>
+      <c r="D144" s="807"/>
       <c r="E144" s="138"/>
       <c r="F144" s="247">
         <v>185900000000</v>
@@ -43999,7 +44008,7 @@
         <v>689</v>
       </c>
       <c r="C145" s="362"/>
-      <c r="D145" s="805"/>
+      <c r="D145" s="807"/>
       <c r="E145" s="138"/>
       <c r="F145" s="247">
         <v>23400000000</v>
@@ -44015,7 +44024,7 @@
         <v>691</v>
       </c>
       <c r="C146" s="362"/>
-      <c r="D146" s="805"/>
+      <c r="D146" s="807"/>
       <c r="E146" s="138"/>
       <c r="F146" s="247">
         <v>69999968880</v>
@@ -44031,7 +44040,7 @@
         <v>690</v>
       </c>
       <c r="C147" s="362"/>
-      <c r="D147" s="805"/>
+      <c r="D147" s="807"/>
       <c r="E147" s="138"/>
       <c r="F147" s="247">
         <v>19710000000</v>
@@ -44047,7 +44056,7 @@
         <v>693</v>
       </c>
       <c r="C148" s="362"/>
-      <c r="D148" s="805"/>
+      <c r="D148" s="807"/>
       <c r="E148" s="138"/>
       <c r="F148" s="247">
         <f>16208369726-3168609726</f>
@@ -44067,7 +44076,7 @@
         <v>662</v>
       </c>
       <c r="C149" s="362"/>
-      <c r="D149" s="805"/>
+      <c r="D149" s="807"/>
       <c r="E149" s="138"/>
       <c r="F149" s="247">
         <f>24057940000+2752000000</f>
@@ -44101,20 +44110,20 @@
     </row>
     <row r="151" spans="1:16" ht="21" customHeight="1" thickTop="1">
       <c r="A151" s="318"/>
-      <c r="B151" s="807"/>
-      <c r="C151" s="807"/>
-      <c r="D151" s="807"/>
-      <c r="E151" s="807"/>
-      <c r="F151" s="807"/>
-      <c r="G151" s="807"/>
-      <c r="H151" s="807"/>
-      <c r="J151" s="806"/>
-      <c r="K151" s="807"/>
-      <c r="L151" s="807"/>
-      <c r="M151" s="807"/>
-      <c r="N151" s="807"/>
-      <c r="O151" s="807"/>
-      <c r="P151" s="807"/>
+      <c r="B151" s="809"/>
+      <c r="C151" s="809"/>
+      <c r="D151" s="809"/>
+      <c r="E151" s="809"/>
+      <c r="F151" s="809"/>
+      <c r="G151" s="809"/>
+      <c r="H151" s="809"/>
+      <c r="J151" s="808"/>
+      <c r="K151" s="809"/>
+      <c r="L151" s="809"/>
+      <c r="M151" s="809"/>
+      <c r="N151" s="809"/>
+      <c r="O151" s="809"/>
+      <c r="P151" s="809"/>
     </row>
     <row r="152" spans="1:16" ht="22.5" customHeight="1" thickBot="1">
       <c r="A152" s="369" t="s">
@@ -44152,7 +44161,7 @@
         <v>838</v>
       </c>
       <c r="C154" s="362"/>
-      <c r="D154" s="805"/>
+      <c r="D154" s="807"/>
       <c r="E154" s="138"/>
       <c r="F154" s="247">
         <v>17221854597</v>
@@ -44166,7 +44175,7 @@
         <v>839</v>
       </c>
       <c r="C155" s="362"/>
-      <c r="D155" s="805"/>
+      <c r="D155" s="807"/>
       <c r="E155" s="138"/>
       <c r="F155" s="247">
         <f>'دارایی ثابت مشهود'!G10</f>
@@ -44181,7 +44190,7 @@
         <v>840</v>
       </c>
       <c r="C156" s="362"/>
-      <c r="D156" s="805"/>
+      <c r="D156" s="807"/>
       <c r="E156" s="138"/>
       <c r="F156" s="295">
         <f>'دارایی ثابت مشهود'!F10</f>
@@ -44209,13 +44218,13 @@
     </row>
     <row r="158" spans="1:16" ht="29.25" customHeight="1" thickTop="1">
       <c r="A158" s="318"/>
-      <c r="B158" s="817"/>
-      <c r="C158" s="817"/>
-      <c r="D158" s="817"/>
-      <c r="E158" s="817"/>
-      <c r="F158" s="817"/>
-      <c r="G158" s="817"/>
-      <c r="H158" s="817"/>
+      <c r="B158" s="818"/>
+      <c r="C158" s="818"/>
+      <c r="D158" s="818"/>
+      <c r="E158" s="818"/>
+      <c r="F158" s="818"/>
+      <c r="G158" s="818"/>
+      <c r="H158" s="818"/>
       <c r="J158" s="169"/>
     </row>
     <row r="159" spans="1:16" ht="22.5" customHeight="1" thickBot="1">
@@ -44258,7 +44267,7 @@
         <v>666</v>
       </c>
       <c r="C161" s="362"/>
-      <c r="D161" s="805"/>
+      <c r="D161" s="807"/>
       <c r="E161" s="138"/>
       <c r="F161" s="247">
         <v>462000000</v>
@@ -44274,7 +44283,7 @@
         <v>667</v>
       </c>
       <c r="C162" s="362"/>
-      <c r="D162" s="805"/>
+      <c r="D162" s="807"/>
       <c r="E162" s="138"/>
       <c r="F162" s="247">
         <v>276000000</v>
@@ -44290,7 +44299,7 @@
         <v>668</v>
       </c>
       <c r="C163" s="362"/>
-      <c r="D163" s="805"/>
+      <c r="D163" s="807"/>
       <c r="E163" s="138"/>
       <c r="F163" s="247">
         <f>4569615500+200000000</f>
@@ -44363,7 +44372,7 @@
         <v>838</v>
       </c>
       <c r="C168" s="362"/>
-      <c r="D168" s="805" t="s">
+      <c r="D168" s="807" t="s">
         <v>677</v>
       </c>
       <c r="E168" s="138"/>
@@ -44380,7 +44389,7 @@
         <v>843</v>
       </c>
       <c r="C169" s="362"/>
-      <c r="D169" s="805"/>
+      <c r="D169" s="807"/>
       <c r="E169" s="138"/>
       <c r="F169" s="295">
         <f>'دارایی ثابت مشهود'!F12</f>
@@ -45124,29 +45133,29 @@
       <c r="A211" s="759" t="s">
         <v>704</v>
       </c>
-      <c r="B211" s="804" t="s">
+      <c r="B211" s="806" t="s">
         <v>848</v>
       </c>
-      <c r="C211" s="804"/>
-      <c r="D211" s="804"/>
-      <c r="E211" s="804"/>
-      <c r="F211" s="804"/>
-      <c r="G211" s="804"/>
-      <c r="H211" s="804"/>
+      <c r="C211" s="806"/>
+      <c r="D211" s="806"/>
+      <c r="E211" s="806"/>
+      <c r="F211" s="806"/>
+      <c r="G211" s="806"/>
+      <c r="H211" s="806"/>
     </row>
     <row r="212" spans="1:13" s="37" customFormat="1" ht="113.25" customHeight="1">
       <c r="A212" s="759" t="s">
         <v>812</v>
       </c>
-      <c r="B212" s="804" t="s">
+      <c r="B212" s="806" t="s">
         <v>971</v>
       </c>
-      <c r="C212" s="804"/>
-      <c r="D212" s="804"/>
-      <c r="E212" s="804"/>
-      <c r="F212" s="804"/>
-      <c r="G212" s="804"/>
-      <c r="H212" s="804"/>
+      <c r="C212" s="806"/>
+      <c r="D212" s="806"/>
+      <c r="E212" s="806"/>
+      <c r="F212" s="806"/>
+      <c r="G212" s="806"/>
+      <c r="H212" s="806"/>
       <c r="J212" s="248"/>
       <c r="K212" s="172"/>
     </row>
@@ -46230,15 +46239,15 @@
     </row>
     <row r="284" spans="1:10" s="588" customFormat="1" ht="57.75" customHeight="1" thickTop="1">
       <c r="A284" s="587"/>
-      <c r="B284" s="818" t="s">
+      <c r="B284" s="819" t="s">
         <v>527</v>
       </c>
-      <c r="C284" s="818"/>
-      <c r="D284" s="818"/>
-      <c r="E284" s="818"/>
-      <c r="F284" s="818"/>
-      <c r="G284" s="818"/>
-      <c r="H284" s="818"/>
+      <c r="C284" s="819"/>
+      <c r="D284" s="819"/>
+      <c r="E284" s="819"/>
+      <c r="F284" s="819"/>
+      <c r="G284" s="819"/>
+      <c r="H284" s="819"/>
     </row>
     <row r="285" spans="1:10" s="36" customFormat="1">
       <c r="A285" s="249"/>
@@ -46368,15 +46377,15 @@
     </row>
     <row r="293" spans="1:11" s="36" customFormat="1" ht="50.25" customHeight="1" thickTop="1">
       <c r="A293" s="249"/>
-      <c r="B293" s="804" t="s">
+      <c r="B293" s="806" t="s">
         <v>808</v>
       </c>
-      <c r="C293" s="804"/>
-      <c r="D293" s="804"/>
-      <c r="E293" s="804"/>
-      <c r="F293" s="804"/>
-      <c r="G293" s="804"/>
-      <c r="H293" s="804"/>
+      <c r="C293" s="806"/>
+      <c r="D293" s="806"/>
+      <c r="E293" s="806"/>
+      <c r="F293" s="806"/>
+      <c r="G293" s="806"/>
+      <c r="H293" s="806"/>
     </row>
     <row r="294" spans="1:11" s="36" customFormat="1">
       <c r="A294" s="249"/>
@@ -46554,7 +46563,7 @@
         <v>226</v>
       </c>
       <c r="C305" s="502"/>
-      <c r="D305" s="811">
+      <c r="D305" s="764">
         <v>30</v>
       </c>
       <c r="E305" s="206"/>
@@ -46573,7 +46582,7 @@
         <v>227</v>
       </c>
       <c r="C306" s="502"/>
-      <c r="D306" s="811"/>
+      <c r="D306" s="764"/>
       <c r="E306" s="206"/>
       <c r="F306" s="247">
         <v>22918598586</v>
@@ -46589,7 +46598,7 @@
         <v>228</v>
       </c>
       <c r="C307" s="502"/>
-      <c r="D307" s="811"/>
+      <c r="D307" s="764"/>
       <c r="E307" s="206"/>
       <c r="F307" s="247">
         <f>ابلاغي!E6</f>
@@ -46661,7 +46670,7 @@
         <v>232</v>
       </c>
       <c r="C312" s="375"/>
-      <c r="D312" s="812" t="s">
+      <c r="D312" s="813" t="s">
         <v>976</v>
       </c>
       <c r="E312" s="247"/>
@@ -46679,7 +46688,7 @@
         <v>233</v>
       </c>
       <c r="C313" s="375"/>
-      <c r="D313" s="812"/>
+      <c r="D313" s="813"/>
       <c r="E313" s="247"/>
       <c r="F313" s="247">
         <f>ابلاغي!E15+'وجوه مصرف نشده'!H26</f>
@@ -48611,148 +48620,148 @@
       <c r="L418"/>
     </row>
     <row r="419" spans="1:12" s="36" customFormat="1" ht="25.5">
-      <c r="A419" s="808" t="s">
+      <c r="A419" s="810" t="s">
         <v>517</v>
       </c>
-      <c r="B419" s="808"/>
-      <c r="C419" s="808"/>
-      <c r="D419" s="808"/>
-      <c r="E419" s="808"/>
-      <c r="F419" s="808"/>
-      <c r="G419" s="808"/>
-      <c r="H419" s="808"/>
+      <c r="B419" s="810"/>
+      <c r="C419" s="810"/>
+      <c r="D419" s="810"/>
+      <c r="E419" s="810"/>
+      <c r="F419" s="810"/>
+      <c r="G419" s="810"/>
+      <c r="H419" s="810"/>
     </row>
     <row r="420" spans="1:12" s="36" customFormat="1" ht="25.5">
-      <c r="A420" s="808" t="s">
+      <c r="A420" s="810" t="s">
         <v>518</v>
       </c>
-      <c r="B420" s="808"/>
-      <c r="C420" s="808"/>
-      <c r="D420" s="808"/>
-      <c r="E420" s="808"/>
-      <c r="F420" s="808"/>
-      <c r="G420" s="808"/>
-      <c r="H420" s="808"/>
+      <c r="B420" s="810"/>
+      <c r="C420" s="810"/>
+      <c r="D420" s="810"/>
+      <c r="E420" s="810"/>
+      <c r="F420" s="810"/>
+      <c r="G420" s="810"/>
+      <c r="H420" s="810"/>
     </row>
     <row r="421" spans="1:12" s="36" customFormat="1" ht="25.5">
-      <c r="A421" s="808" t="s">
+      <c r="A421" s="810" t="s">
         <v>518</v>
       </c>
-      <c r="B421" s="808"/>
-      <c r="C421" s="808"/>
-      <c r="D421" s="808"/>
-      <c r="E421" s="808"/>
-      <c r="F421" s="808"/>
-      <c r="G421" s="808"/>
-      <c r="H421" s="808"/>
+      <c r="B421" s="810"/>
+      <c r="C421" s="810"/>
+      <c r="D421" s="810"/>
+      <c r="E421" s="810"/>
+      <c r="F421" s="810"/>
+      <c r="G421" s="810"/>
+      <c r="H421" s="810"/>
     </row>
     <row r="422" spans="1:12" s="36" customFormat="1" ht="25.5">
-      <c r="A422" s="808" t="s">
+      <c r="A422" s="810" t="s">
         <v>518</v>
       </c>
-      <c r="B422" s="808"/>
-      <c r="C422" s="808"/>
-      <c r="D422" s="808"/>
-      <c r="E422" s="808"/>
-      <c r="F422" s="808"/>
-      <c r="G422" s="808"/>
-      <c r="H422" s="808"/>
+      <c r="B422" s="810"/>
+      <c r="C422" s="810"/>
+      <c r="D422" s="810"/>
+      <c r="E422" s="810"/>
+      <c r="F422" s="810"/>
+      <c r="G422" s="810"/>
+      <c r="H422" s="810"/>
     </row>
     <row r="423" spans="1:12" s="36" customFormat="1" ht="25.5">
-      <c r="A423" s="808" t="s">
+      <c r="A423" s="810" t="s">
         <v>518</v>
       </c>
-      <c r="B423" s="808"/>
-      <c r="C423" s="808"/>
-      <c r="D423" s="808"/>
-      <c r="E423" s="808"/>
-      <c r="F423" s="808"/>
-      <c r="G423" s="808"/>
-      <c r="H423" s="808"/>
+      <c r="B423" s="810"/>
+      <c r="C423" s="810"/>
+      <c r="D423" s="810"/>
+      <c r="E423" s="810"/>
+      <c r="F423" s="810"/>
+      <c r="G423" s="810"/>
+      <c r="H423" s="810"/>
     </row>
     <row r="424" spans="1:12" s="36" customFormat="1" ht="25.5">
-      <c r="A424" s="808" t="s">
+      <c r="A424" s="810" t="s">
         <v>519</v>
       </c>
-      <c r="B424" s="808"/>
-      <c r="C424" s="808"/>
-      <c r="D424" s="808"/>
-      <c r="E424" s="808"/>
-      <c r="F424" s="808"/>
-      <c r="G424" s="808"/>
-      <c r="H424" s="808"/>
+      <c r="B424" s="810"/>
+      <c r="C424" s="810"/>
+      <c r="D424" s="810"/>
+      <c r="E424" s="810"/>
+      <c r="F424" s="810"/>
+      <c r="G424" s="810"/>
+      <c r="H424" s="810"/>
     </row>
     <row r="425" spans="1:12" s="36" customFormat="1" ht="25.5">
-      <c r="A425" s="808" t="s">
+      <c r="A425" s="810" t="s">
         <v>519</v>
       </c>
-      <c r="B425" s="808"/>
-      <c r="C425" s="808"/>
-      <c r="D425" s="808"/>
-      <c r="E425" s="808"/>
-      <c r="F425" s="808"/>
-      <c r="G425" s="808"/>
-      <c r="H425" s="808"/>
+      <c r="B425" s="810"/>
+      <c r="C425" s="810"/>
+      <c r="D425" s="810"/>
+      <c r="E425" s="810"/>
+      <c r="F425" s="810"/>
+      <c r="G425" s="810"/>
+      <c r="H425" s="810"/>
     </row>
     <row r="426" spans="1:12" s="36" customFormat="1" ht="25.5">
-      <c r="A426" s="808" t="s">
+      <c r="A426" s="810" t="s">
         <v>520</v>
       </c>
-      <c r="B426" s="808"/>
-      <c r="C426" s="808"/>
-      <c r="D426" s="808"/>
-      <c r="E426" s="808"/>
-      <c r="F426" s="808"/>
-      <c r="G426" s="808"/>
-      <c r="H426" s="808"/>
+      <c r="B426" s="810"/>
+      <c r="C426" s="810"/>
+      <c r="D426" s="810"/>
+      <c r="E426" s="810"/>
+      <c r="F426" s="810"/>
+      <c r="G426" s="810"/>
+      <c r="H426" s="810"/>
     </row>
     <row r="427" spans="1:12" s="36" customFormat="1" ht="25.5">
-      <c r="A427" s="808" t="s">
+      <c r="A427" s="810" t="s">
         <v>520</v>
       </c>
-      <c r="B427" s="808"/>
-      <c r="C427" s="808"/>
-      <c r="D427" s="808"/>
-      <c r="E427" s="808"/>
-      <c r="F427" s="808"/>
-      <c r="G427" s="808"/>
-      <c r="H427" s="808"/>
+      <c r="B427" s="810"/>
+      <c r="C427" s="810"/>
+      <c r="D427" s="810"/>
+      <c r="E427" s="810"/>
+      <c r="F427" s="810"/>
+      <c r="G427" s="810"/>
+      <c r="H427" s="810"/>
     </row>
     <row r="428" spans="1:12" s="36" customFormat="1" ht="25.5">
-      <c r="A428" s="808" t="s">
+      <c r="A428" s="810" t="s">
         <v>521</v>
       </c>
-      <c r="B428" s="808"/>
-      <c r="C428" s="808"/>
-      <c r="D428" s="808"/>
-      <c r="E428" s="808"/>
-      <c r="F428" s="808"/>
-      <c r="G428" s="808"/>
-      <c r="H428" s="808"/>
+      <c r="B428" s="810"/>
+      <c r="C428" s="810"/>
+      <c r="D428" s="810"/>
+      <c r="E428" s="810"/>
+      <c r="F428" s="810"/>
+      <c r="G428" s="810"/>
+      <c r="H428" s="810"/>
     </row>
     <row r="429" spans="1:12" s="36" customFormat="1" ht="25.5">
-      <c r="A429" s="808" t="s">
+      <c r="A429" s="810" t="s">
         <v>521</v>
       </c>
-      <c r="B429" s="808"/>
-      <c r="C429" s="808"/>
-      <c r="D429" s="808"/>
-      <c r="E429" s="808"/>
-      <c r="F429" s="808"/>
-      <c r="G429" s="808"/>
-      <c r="H429" s="808"/>
+      <c r="B429" s="810"/>
+      <c r="C429" s="810"/>
+      <c r="D429" s="810"/>
+      <c r="E429" s="810"/>
+      <c r="F429" s="810"/>
+      <c r="G429" s="810"/>
+      <c r="H429" s="810"/>
     </row>
     <row r="430" spans="1:12" s="36" customFormat="1" ht="25.5">
-      <c r="A430" s="808" t="s">
+      <c r="A430" s="810" t="s">
         <v>522</v>
       </c>
-      <c r="B430" s="808"/>
-      <c r="C430" s="808"/>
-      <c r="D430" s="808"/>
-      <c r="E430" s="808"/>
-      <c r="F430" s="808"/>
-      <c r="G430" s="808"/>
-      <c r="H430" s="808"/>
+      <c r="B430" s="810"/>
+      <c r="C430" s="810"/>
+      <c r="D430" s="810"/>
+      <c r="E430" s="810"/>
+      <c r="F430" s="810"/>
+      <c r="G430" s="810"/>
+      <c r="H430" s="810"/>
     </row>
     <row r="431" spans="1:12" s="36" customFormat="1" ht="27" customHeight="1">
       <c r="A431" s="261"/>
@@ -49142,13 +49151,13 @@
     </row>
     <row r="462" spans="1:10" s="562" customFormat="1">
       <c r="A462" s="563"/>
-      <c r="B462" s="809" t="s">
+      <c r="B462" s="811" t="s">
         <v>695</v>
       </c>
-      <c r="C462" s="809"/>
-      <c r="D462" s="809"/>
-      <c r="E462" s="809"/>
-      <c r="F462" s="809"/>
+      <c r="C462" s="811"/>
+      <c r="D462" s="811"/>
+      <c r="E462" s="811"/>
+      <c r="F462" s="811"/>
       <c r="G462" s="370"/>
       <c r="H462" s="370"/>
       <c r="I462" s="561"/>
@@ -49194,13 +49203,13 @@
     </row>
     <row r="466" spans="1:9" s="458" customFormat="1">
       <c r="A466" s="368"/>
-      <c r="B466" s="809" t="s">
+      <c r="B466" s="811" t="s">
         <v>526</v>
       </c>
-      <c r="C466" s="809"/>
-      <c r="D466" s="809"/>
-      <c r="E466" s="809"/>
-      <c r="F466" s="809"/>
+      <c r="C466" s="811"/>
+      <c r="D466" s="811"/>
+      <c r="E466" s="811"/>
+      <c r="F466" s="811"/>
       <c r="G466" s="138"/>
       <c r="H466" s="138"/>
       <c r="I466" s="566"/>
@@ -49656,11 +49665,11 @@
     </row>
     <row r="30" spans="1:8" s="562" customFormat="1" ht="27">
       <c r="A30" s="563"/>
-      <c r="B30" s="809" t="s">
+      <c r="B30" s="811" t="s">
         <v>695</v>
       </c>
-      <c r="C30" s="809"/>
-      <c r="D30" s="809"/>
+      <c r="C30" s="811"/>
+      <c r="D30" s="811"/>
       <c r="E30" s="370"/>
       <c r="F30" s="370"/>
       <c r="G30" s="561"/>
@@ -49700,11 +49709,11 @@
     </row>
     <row r="34" spans="1:7" s="458" customFormat="1" ht="27">
       <c r="A34" s="368"/>
-      <c r="B34" s="809" t="s">
+      <c r="B34" s="811" t="s">
         <v>526</v>
       </c>
-      <c r="C34" s="809"/>
-      <c r="D34" s="809"/>
+      <c r="C34" s="811"/>
+      <c r="D34" s="811"/>
       <c r="E34" s="138"/>
       <c r="F34" s="138"/>
       <c r="G34" s="566"/>
